--- a/src/dev/MS-OXPROPS-250520.xlsx
+++ b/src/dev/MS-OXPROPS-250520.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\hrag\Sync\Programming\rust\pst_reader\src\dev\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\hrag\Sync\Programming\rust\pst-reader\src\dev\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F9F35106-92AF-4C4C-A530-99FC4A04E215}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{42E01936-837A-47B9-A614-B5102B5EC504}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="8550" yWindow="4545" windowWidth="28800" windowHeight="15345" xr2:uid="{8BE28B03-08C2-499B-8EA3-73C05A551F5B}"/>
+    <workbookView xWindow="2340" yWindow="2340" windowWidth="21600" windowHeight="12645" xr2:uid="{8BE28B03-08C2-499B-8EA3-73C05A551F5B}"/>
   </bookViews>
   <sheets>
     <sheet name="(MS-OXPROPS)-250520" sheetId="1" r:id="rId1"/>
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3464" uniqueCount="2323">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3465" uniqueCount="2324">
   <si>
     <t>Canonical name</t>
   </si>
@@ -7002,6 +7002,9 @@
   </si>
   <si>
     <t>enum</t>
+  </si>
+  <si>
+    <t>PidTagNonReceiptNotificationRequested</t>
   </si>
 </sst>
 </file>
@@ -15103,7 +15106,7 @@
         <v>1063</v>
       </c>
       <c r="D259" t="str">
-        <f t="shared" ref="D259:D309" si="8">RIGHT(C259,LEN(C259)-6)</f>
+        <f t="shared" ref="D259:D322" si="8">RIGHT(C259,LEN(C259)-6)</f>
         <v>JunkPhishingEnableLinks</v>
       </c>
       <c r="E259" t="s">
@@ -15116,7 +15119,7 @@
         <v>1066</v>
       </c>
       <c r="H259" t="str">
-        <f t="shared" ref="H259:H270" si="9">D259 &amp; " = " &amp; A259 &amp; ","</f>
+        <f t="shared" ref="H259:H322" si="9">D259 &amp; " = " &amp; A259 &amp; ","</f>
         <v>JunkPhishingEnableLinks = 0x6107,</v>
       </c>
     </row>
@@ -15448,6 +15451,10 @@
       <c r="F271" t="s">
         <v>691</v>
       </c>
+      <c r="H271" t="str">
+        <f t="shared" si="9"/>
+        <v>LocalCommitTime = 0x6709,</v>
+      </c>
     </row>
     <row r="272" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A272" t="s">
@@ -15472,8 +15479,12 @@
       <c r="G272" t="s">
         <v>1117</v>
       </c>
-    </row>
-    <row r="273" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H272" t="str">
+        <f t="shared" si="9"/>
+        <v>LocalCommitTimeMax = 0x670A,</v>
+      </c>
+    </row>
+    <row r="273" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A273" t="s">
         <v>1120</v>
       </c>
@@ -15496,8 +15507,12 @@
       <c r="G273" t="s">
         <v>1121</v>
       </c>
-    </row>
-    <row r="274" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H273" t="str">
+        <f t="shared" si="9"/>
+        <v>LocaleId = 0x66A1,</v>
+      </c>
+    </row>
+    <row r="274" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A274" t="s">
         <v>1124</v>
       </c>
@@ -15520,8 +15535,12 @@
       <c r="G274" t="s">
         <v>1125</v>
       </c>
-    </row>
-    <row r="275" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H274" t="str">
+        <f t="shared" si="9"/>
+        <v>Locality = 0x3A27,</v>
+      </c>
+    </row>
+    <row r="275" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A275" t="s">
         <v>1128</v>
       </c>
@@ -15544,8 +15563,12 @@
       <c r="G275" t="s">
         <v>1129</v>
       </c>
-    </row>
-    <row r="276" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H275" t="str">
+        <f t="shared" si="9"/>
+        <v>Location = 0x3A0D,</v>
+      </c>
+    </row>
+    <row r="276" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A276" t="s">
         <v>1132</v>
       </c>
@@ -15568,8 +15591,12 @@
       <c r="G276" t="s">
         <v>1134</v>
       </c>
-    </row>
-    <row r="277" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H276" t="str">
+        <f t="shared" si="9"/>
+        <v>MailboxOwnerEntryId = 0x661B,</v>
+      </c>
+    </row>
+    <row r="277" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A277" t="s">
         <v>1137</v>
       </c>
@@ -15592,8 +15619,12 @@
       <c r="G277" t="s">
         <v>1138</v>
       </c>
-    </row>
-    <row r="278" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H277" t="str">
+        <f t="shared" si="9"/>
+        <v>MailboxOwnerName = 0x661C,</v>
+      </c>
+    </row>
+    <row r="278" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A278" t="s">
         <v>1141</v>
       </c>
@@ -15616,8 +15647,12 @@
       <c r="G278" t="s">
         <v>1142</v>
       </c>
-    </row>
-    <row r="279" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H278" t="str">
+        <f t="shared" si="9"/>
+        <v>ManagerName = 0x3A4E,</v>
+      </c>
+    </row>
+    <row r="279" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A279" t="s">
         <v>1145</v>
       </c>
@@ -15640,8 +15675,12 @@
       <c r="G279" t="s">
         <v>1146</v>
       </c>
-    </row>
-    <row r="280" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H279" t="str">
+        <f t="shared" si="9"/>
+        <v>MappingSignature = 0x0FF8,</v>
+      </c>
+    </row>
+    <row r="280" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A280" t="s">
         <v>1149</v>
       </c>
@@ -15664,8 +15703,12 @@
       <c r="G280" t="s">
         <v>1150</v>
       </c>
-    </row>
-    <row r="281" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H280" t="str">
+        <f t="shared" si="9"/>
+        <v>MaximumSubmitMessageSize = 0x666D,</v>
+      </c>
+    </row>
+    <row r="281" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A281" t="s">
         <v>1153</v>
       </c>
@@ -15688,8 +15731,12 @@
       <c r="G281" t="s">
         <v>1154</v>
       </c>
-    </row>
-    <row r="282" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H281" t="str">
+        <f t="shared" si="9"/>
+        <v>MemberId = 0x6671,</v>
+      </c>
+    </row>
+    <row r="282" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A282" t="s">
         <v>1157</v>
       </c>
@@ -15712,8 +15759,12 @@
       <c r="G282" t="s">
         <v>1158</v>
       </c>
-    </row>
-    <row r="283" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H282" t="str">
+        <f t="shared" si="9"/>
+        <v>MemberName = 0x6672,</v>
+      </c>
+    </row>
+    <row r="283" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A283" t="s">
         <v>1161</v>
       </c>
@@ -15736,8 +15787,12 @@
       <c r="G283" t="s">
         <v>1162</v>
       </c>
-    </row>
-    <row r="284" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H283" t="str">
+        <f t="shared" si="9"/>
+        <v>MemberRights = 0x6673,</v>
+      </c>
+    </row>
+    <row r="284" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A284" t="s">
         <v>1165</v>
       </c>
@@ -15760,8 +15815,12 @@
       <c r="G284" t="s">
         <v>1166</v>
       </c>
-    </row>
-    <row r="285" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H284" t="str">
+        <f t="shared" si="9"/>
+        <v>MessageAttachments = 0x0E13,</v>
+      </c>
+    </row>
+    <row r="285" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A285" t="s">
         <v>1168</v>
       </c>
@@ -15781,8 +15840,12 @@
       <c r="G285" t="s">
         <v>1169</v>
       </c>
-    </row>
-    <row r="286" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H285" t="str">
+        <f t="shared" si="9"/>
+        <v>MessageCcMe = 0x0058,</v>
+      </c>
+    </row>
+    <row r="286" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A286" t="s">
         <v>1172</v>
       </c>
@@ -15805,8 +15868,12 @@
       <c r="G286" t="s">
         <v>1174</v>
       </c>
-    </row>
-    <row r="287" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H286" t="str">
+        <f t="shared" si="9"/>
+        <v>MessageClass = 0x001A,</v>
+      </c>
+    </row>
+    <row r="287" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A287" t="s">
         <v>1177</v>
       </c>
@@ -15829,8 +15896,12 @@
       <c r="G287" t="s">
         <v>1178</v>
       </c>
-    </row>
-    <row r="288" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H287" t="str">
+        <f t="shared" si="9"/>
+        <v>MessageCodepage = 0x3FFD,</v>
+      </c>
+    </row>
+    <row r="288" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A288" t="s">
         <v>1181</v>
       </c>
@@ -15853,8 +15924,12 @@
       <c r="G288" t="s">
         <v>1182</v>
       </c>
-    </row>
-    <row r="289" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H288" t="str">
+        <f t="shared" si="9"/>
+        <v>MessageDeliveryTime = 0x0E06,</v>
+      </c>
+    </row>
+    <row r="289" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A289" t="s">
         <v>1185</v>
       </c>
@@ -15877,8 +15952,12 @@
       <c r="G289" t="s">
         <v>1186</v>
       </c>
-    </row>
-    <row r="290" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H289" t="str">
+        <f t="shared" si="9"/>
+        <v>MessageEditorFormat = 0x5909,</v>
+      </c>
+    </row>
+    <row r="290" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A290" t="s">
         <v>1189</v>
       </c>
@@ -15901,8 +15980,12 @@
       <c r="G290" t="s">
         <v>1190</v>
       </c>
-    </row>
-    <row r="291" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H290" t="str">
+        <f t="shared" si="9"/>
+        <v>MessageFlags = 0x0E07,</v>
+      </c>
+    </row>
+    <row r="291" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A291" t="s">
         <v>1193</v>
       </c>
@@ -15925,8 +16008,12 @@
       <c r="G291" t="s">
         <v>1194</v>
       </c>
-    </row>
-    <row r="292" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H291" t="str">
+        <f t="shared" si="9"/>
+        <v>MessageHandlingSystemCommonName = 0x3A0F,</v>
+      </c>
+    </row>
+    <row r="292" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A292" t="s">
         <v>1197</v>
       </c>
@@ -15949,8 +16036,12 @@
       <c r="G292" t="s">
         <v>1198</v>
       </c>
-    </row>
-    <row r="293" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H292" t="str">
+        <f t="shared" si="9"/>
+        <v>MessageLocaleId = 0x3FF1,</v>
+      </c>
+    </row>
+    <row r="293" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A293" t="s">
         <v>1201</v>
       </c>
@@ -15973,8 +16064,12 @@
       <c r="G293" t="s">
         <v>1202</v>
       </c>
-    </row>
-    <row r="294" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H293" t="str">
+        <f t="shared" si="9"/>
+        <v>MessageRecipientMe = 0x0059,</v>
+      </c>
+    </row>
+    <row r="294" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A294" t="s">
         <v>1205</v>
       </c>
@@ -15997,8 +16092,12 @@
       <c r="G294" t="s">
         <v>1206</v>
       </c>
-    </row>
-    <row r="295" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H294" t="str">
+        <f t="shared" si="9"/>
+        <v>MessageRecipients = 0x0E12,</v>
+      </c>
+    </row>
+    <row r="295" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A295" t="s">
         <v>1209</v>
       </c>
@@ -16021,8 +16120,12 @@
       <c r="G295" t="s">
         <v>1210</v>
       </c>
-    </row>
-    <row r="296" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H295" t="str">
+        <f t="shared" si="9"/>
+        <v>MessageSize = 0x0E08,</v>
+      </c>
+    </row>
+    <row r="296" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A296" t="s">
         <v>1209</v>
       </c>
@@ -16045,8 +16148,12 @@
       <c r="G296" t="s">
         <v>1213</v>
       </c>
-    </row>
-    <row r="297" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H296" t="str">
+        <f t="shared" si="9"/>
+        <v>MessageSizeExtended = 0x0E08,</v>
+      </c>
+    </row>
+    <row r="297" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A297" t="s">
         <v>1216</v>
       </c>
@@ -16069,8 +16176,12 @@
       <c r="G297" t="s">
         <v>1217</v>
       </c>
-    </row>
-    <row r="298" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H297" t="str">
+        <f t="shared" si="9"/>
+        <v>MessageStatus = 0x0E17,</v>
+      </c>
+    </row>
+    <row r="298" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A298" t="s">
         <v>1220</v>
       </c>
@@ -16093,8 +16204,12 @@
       <c r="G298" t="s">
         <v>1221</v>
       </c>
-    </row>
-    <row r="299" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H298" t="str">
+        <f t="shared" si="9"/>
+        <v>MessageSubmissionId = 0x0047,</v>
+      </c>
+    </row>
+    <row r="299" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A299" t="s">
         <v>1224</v>
       </c>
@@ -16117,8 +16232,12 @@
       <c r="G299" t="s">
         <v>1225</v>
       </c>
-    </row>
-    <row r="300" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H299" t="str">
+        <f t="shared" si="9"/>
+        <v>MessageToMe = 0x0057,</v>
+      </c>
+    </row>
+    <row r="300" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A300" t="s">
         <v>1228</v>
       </c>
@@ -16141,8 +16260,12 @@
       <c r="G300" t="s">
         <v>1229</v>
       </c>
-    </row>
-    <row r="301" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H300" t="str">
+        <f t="shared" si="9"/>
+        <v>Mid = 0x674A,</v>
+      </c>
+    </row>
+    <row r="301" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A301" t="s">
         <v>1232</v>
       </c>
@@ -16165,8 +16288,12 @@
       <c r="G301" t="s">
         <v>1233</v>
       </c>
-    </row>
-    <row r="302" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H301" t="str">
+        <f t="shared" si="9"/>
+        <v>MiddleName = 0x3A44,</v>
+      </c>
+    </row>
+    <row r="302" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A302" t="s">
         <v>1236</v>
       </c>
@@ -16189,8 +16316,12 @@
       <c r="G302" t="s">
         <v>1238</v>
       </c>
-    </row>
-    <row r="303" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H302" t="str">
+        <f t="shared" si="9"/>
+        <v>MimeSkeleton = 0x64F0,</v>
+      </c>
+    </row>
+    <row r="303" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A303" t="s">
         <v>1241</v>
       </c>
@@ -16213,8 +16344,12 @@
       <c r="G303" t="s">
         <v>1242</v>
       </c>
-    </row>
-    <row r="304" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H303" t="str">
+        <f t="shared" si="9"/>
+        <v>MobileTelephoneNumber = 0x3A1C,</v>
+      </c>
+    </row>
+    <row r="304" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A304" t="s">
         <v>1245</v>
       </c>
@@ -16237,8 +16372,12 @@
       <c r="G304" t="s">
         <v>1247</v>
       </c>
-    </row>
-    <row r="305" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H304" t="str">
+        <f t="shared" si="9"/>
+        <v>NativeBody = 0x1016,</v>
+      </c>
+    </row>
+    <row r="305" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A305" t="s">
         <v>1250</v>
       </c>
@@ -16261,8 +16400,12 @@
       <c r="G305" t="s">
         <v>1251</v>
       </c>
-    </row>
-    <row r="306" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H305" t="str">
+        <f t="shared" si="9"/>
+        <v>NextSendAcct = 0x0E29,</v>
+      </c>
+    </row>
+    <row r="306" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A306" t="s">
         <v>1254</v>
       </c>
@@ -16285,8 +16428,12 @@
       <c r="G306" t="s">
         <v>1255</v>
       </c>
-    </row>
-    <row r="307" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H306" t="str">
+        <f t="shared" si="9"/>
+        <v>Nickname = 0x3A4F,</v>
+      </c>
+    </row>
+    <row r="307" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A307" t="s">
         <v>1258</v>
       </c>
@@ -16309,8 +16456,12 @@
       <c r="G307" t="s">
         <v>1259</v>
       </c>
-    </row>
-    <row r="308" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H307" t="str">
+        <f t="shared" si="9"/>
+        <v>NonDeliveryReportDiagCode = 0x0C05,</v>
+      </c>
+    </row>
+    <row r="308" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A308" t="s">
         <v>1262</v>
       </c>
@@ -16333,8 +16484,12 @@
       <c r="G308" t="s">
         <v>1263</v>
       </c>
-    </row>
-    <row r="309" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H308" t="str">
+        <f t="shared" si="9"/>
+        <v>NonDeliveryReportReasonCode = 0x0C04,</v>
+      </c>
+    </row>
+    <row r="309" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A309" t="s">
         <v>1266</v>
       </c>
@@ -16357,14 +16512,25 @@
       <c r="G309" t="s">
         <v>1267</v>
       </c>
-    </row>
-    <row r="310" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H309" t="str">
+        <f t="shared" si="9"/>
+        <v>NonDeliveryReportStatusCode = 0x0C20,</v>
+      </c>
+    </row>
+    <row r="310" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A310" t="s">
         <v>1269</v>
       </c>
       <c r="B310" t="s">
         <v>10</v>
       </c>
+      <c r="C310" t="s">
+        <v>2323</v>
+      </c>
+      <c r="D310" t="str">
+        <f t="shared" si="8"/>
+        <v>NonReceiptNotificationRequested</v>
+      </c>
       <c r="E310" t="s">
         <v>1268</v>
       </c>
@@ -16374,8 +16540,12 @@
       <c r="G310" t="s">
         <v>1270</v>
       </c>
-    </row>
-    <row r="311" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H310" t="str">
+        <f t="shared" si="9"/>
+        <v>NonReceiptNotificationRequested = 0x0C06,</v>
+      </c>
+    </row>
+    <row r="311" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A311" t="s">
         <v>1273</v>
       </c>
@@ -16385,6 +16555,10 @@
       <c r="C311" t="s">
         <v>1271</v>
       </c>
+      <c r="D311" t="str">
+        <f t="shared" si="8"/>
+        <v>NormalizedSubject</v>
+      </c>
       <c r="E311" t="s">
         <v>1272</v>
       </c>
@@ -16394,8 +16568,12 @@
       <c r="G311" t="s">
         <v>1274</v>
       </c>
-    </row>
-    <row r="312" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H311" t="str">
+        <f t="shared" si="9"/>
+        <v>NormalizedSubject = 0x0E1D,</v>
+      </c>
+    </row>
+    <row r="312" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A312" t="s">
         <v>1277</v>
       </c>
@@ -16405,6 +16583,10 @@
       <c r="C312" t="s">
         <v>1275</v>
       </c>
+      <c r="D312" t="str">
+        <f t="shared" si="8"/>
+        <v>ObjectType</v>
+      </c>
       <c r="E312" t="s">
         <v>1276</v>
       </c>
@@ -16414,8 +16596,12 @@
       <c r="G312" t="s">
         <v>1278</v>
       </c>
-    </row>
-    <row r="313" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H312" t="str">
+        <f t="shared" si="9"/>
+        <v>ObjectType = 0x0FFE,</v>
+      </c>
+    </row>
+    <row r="313" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A313" t="s">
         <v>1281</v>
       </c>
@@ -16425,6 +16611,10 @@
       <c r="C313" t="s">
         <v>1279</v>
       </c>
+      <c r="D313" t="str">
+        <f t="shared" si="8"/>
+        <v>OfficeLocation</v>
+      </c>
       <c r="E313" t="s">
         <v>1280</v>
       </c>
@@ -16434,8 +16624,12 @@
       <c r="G313" t="s">
         <v>1282</v>
       </c>
-    </row>
-    <row r="314" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H313" t="str">
+        <f t="shared" si="9"/>
+        <v>OfficeLocation = 0x3A19,</v>
+      </c>
+    </row>
+    <row r="314" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A314" t="s">
         <v>1285</v>
       </c>
@@ -16445,6 +16639,10 @@
       <c r="C314" t="s">
         <v>1283</v>
       </c>
+      <c r="D314" t="str">
+        <f t="shared" si="8"/>
+        <v>OfflineAddressBookContainerGuid</v>
+      </c>
       <c r="E314" t="s">
         <v>1284</v>
       </c>
@@ -16454,8 +16652,12 @@
       <c r="G314" t="s">
         <v>1287</v>
       </c>
-    </row>
-    <row r="315" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H314" t="str">
+        <f t="shared" si="9"/>
+        <v>OfflineAddressBookContainerGuid = 0x6802,</v>
+      </c>
+    </row>
+    <row r="315" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A315" t="s">
         <v>804</v>
       </c>
@@ -16465,6 +16667,10 @@
       <c r="C315" t="s">
         <v>1288</v>
       </c>
+      <c r="D315" t="str">
+        <f t="shared" si="8"/>
+        <v>OfflineAddressBookDistinguishedName</v>
+      </c>
       <c r="E315" t="s">
         <v>1289</v>
       </c>
@@ -16474,8 +16680,12 @@
       <c r="G315" t="s">
         <v>1290</v>
       </c>
-    </row>
-    <row r="316" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H315" t="str">
+        <f t="shared" si="9"/>
+        <v>OfflineAddressBookDistinguishedName = 0x6804,</v>
+      </c>
+    </row>
+    <row r="316" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A316" t="s">
         <v>1293</v>
       </c>
@@ -16485,6 +16695,10 @@
       <c r="C316" t="s">
         <v>1291</v>
       </c>
+      <c r="D316" t="str">
+        <f t="shared" si="8"/>
+        <v>OfflineAddressBookMessageClass</v>
+      </c>
       <c r="E316" t="s">
         <v>1292</v>
       </c>
@@ -16494,8 +16708,12 @@
       <c r="G316" t="s">
         <v>1294</v>
       </c>
-    </row>
-    <row r="317" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H316" t="str">
+        <f t="shared" si="9"/>
+        <v>OfflineAddressBookMessageClass = 0x6803,</v>
+      </c>
+    </row>
+    <row r="317" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A317" t="s">
         <v>1297</v>
       </c>
@@ -16505,6 +16723,10 @@
       <c r="C317" t="s">
         <v>1295</v>
       </c>
+      <c r="D317" t="str">
+        <f t="shared" si="8"/>
+        <v>OfflineAddressBookName</v>
+      </c>
       <c r="E317" t="s">
         <v>1296</v>
       </c>
@@ -16514,8 +16736,12 @@
       <c r="G317" t="s">
         <v>1298</v>
       </c>
-    </row>
-    <row r="318" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H317" t="str">
+        <f t="shared" si="9"/>
+        <v>OfflineAddressBookName = 0x6800,</v>
+      </c>
+    </row>
+    <row r="318" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A318" t="s">
         <v>1301</v>
       </c>
@@ -16525,6 +16751,10 @@
       <c r="C318" t="s">
         <v>1299</v>
       </c>
+      <c r="D318" t="str">
+        <f t="shared" si="8"/>
+        <v>OfflineAddressBookSequence</v>
+      </c>
       <c r="E318" t="s">
         <v>1300</v>
       </c>
@@ -16534,8 +16764,12 @@
       <c r="G318" t="s">
         <v>1302</v>
       </c>
-    </row>
-    <row r="319" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H318" t="str">
+        <f t="shared" si="9"/>
+        <v>OfflineAddressBookSequence = 0x6801,</v>
+      </c>
+    </row>
+    <row r="319" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A319" t="s">
         <v>1305</v>
       </c>
@@ -16545,6 +16779,10 @@
       <c r="C319" t="s">
         <v>1303</v>
       </c>
+      <c r="D319" t="str">
+        <f t="shared" si="8"/>
+        <v>OfflineAddressBookTruncatedProperties</v>
+      </c>
       <c r="E319" t="s">
         <v>1304</v>
       </c>
@@ -16554,8 +16792,12 @@
       <c r="G319" t="s">
         <v>103</v>
       </c>
-    </row>
-    <row r="320" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H319" t="str">
+        <f t="shared" si="9"/>
+        <v>OfflineAddressBookTruncatedProperties = 0x6805,</v>
+      </c>
+    </row>
+    <row r="320" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A320" t="s">
         <v>1308</v>
       </c>
@@ -16565,6 +16807,10 @@
       <c r="C320" t="s">
         <v>1306</v>
       </c>
+      <c r="D320" t="str">
+        <f t="shared" si="8"/>
+        <v>OrdinalMost</v>
+      </c>
       <c r="E320" t="s">
         <v>1307</v>
       </c>
@@ -16574,8 +16820,12 @@
       <c r="G320" t="s">
         <v>1309</v>
       </c>
-    </row>
-    <row r="321" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H320" t="str">
+        <f t="shared" si="9"/>
+        <v>OrdinalMost = 0x36E2,</v>
+      </c>
+    </row>
+    <row r="321" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A321" t="s">
         <v>1312</v>
       </c>
@@ -16585,6 +16835,10 @@
       <c r="C321" t="s">
         <v>1310</v>
       </c>
+      <c r="D321" t="str">
+        <f t="shared" si="8"/>
+        <v>OrganizationalIdNumber</v>
+      </c>
       <c r="E321" t="s">
         <v>1311</v>
       </c>
@@ -16594,8 +16848,12 @@
       <c r="G321" t="s">
         <v>1313</v>
       </c>
-    </row>
-    <row r="322" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H321" t="str">
+        <f t="shared" si="9"/>
+        <v>OrganizationalIdNumber = 0x3A10,</v>
+      </c>
+    </row>
+    <row r="322" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A322" t="s">
         <v>1316</v>
       </c>
@@ -16605,6 +16863,10 @@
       <c r="C322" t="s">
         <v>1314</v>
       </c>
+      <c r="D322" t="str">
+        <f t="shared" si="8"/>
+        <v>OriginalAuthorEntryId</v>
+      </c>
       <c r="E322" t="s">
         <v>1315</v>
       </c>
@@ -16614,8 +16876,12 @@
       <c r="G322" t="s">
         <v>1317</v>
       </c>
-    </row>
-    <row r="323" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H322" t="str">
+        <f t="shared" si="9"/>
+        <v>OriginalAuthorEntryId = 0x004C,</v>
+      </c>
+    </row>
+    <row r="323" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A323" t="s">
         <v>1320</v>
       </c>
@@ -16625,6 +16891,10 @@
       <c r="C323" t="s">
         <v>1318</v>
       </c>
+      <c r="D323" t="str">
+        <f t="shared" ref="D323:D386" si="10">RIGHT(C323,LEN(C323)-6)</f>
+        <v>OriginalAuthorName</v>
+      </c>
       <c r="E323" t="s">
         <v>1319</v>
       </c>
@@ -16634,8 +16904,12 @@
       <c r="G323" t="s">
         <v>1321</v>
       </c>
-    </row>
-    <row r="324" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H323" t="str">
+        <f t="shared" ref="H323:H386" si="11">D323 &amp; " = " &amp; A323 &amp; ","</f>
+        <v>OriginalAuthorName = 0x004D,</v>
+      </c>
+    </row>
+    <row r="324" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A324" t="s">
         <v>1324</v>
       </c>
@@ -16645,6 +16919,10 @@
       <c r="C324" t="s">
         <v>1322</v>
       </c>
+      <c r="D324" t="str">
+        <f t="shared" si="10"/>
+        <v>OriginalDeliveryTime</v>
+      </c>
       <c r="E324" t="s">
         <v>1323</v>
       </c>
@@ -16654,8 +16932,12 @@
       <c r="G324" t="s">
         <v>1325</v>
       </c>
-    </row>
-    <row r="325" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H324" t="str">
+        <f t="shared" si="11"/>
+        <v>OriginalDeliveryTime = 0x0055,</v>
+      </c>
+    </row>
+    <row r="325" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A325" t="s">
         <v>1328</v>
       </c>
@@ -16665,6 +16947,10 @@
       <c r="C325" t="s">
         <v>1326</v>
       </c>
+      <c r="D325" t="str">
+        <f t="shared" si="10"/>
+        <v>OriginalDisplayBcc</v>
+      </c>
       <c r="E325" t="s">
         <v>1327</v>
       </c>
@@ -16674,8 +16960,12 @@
       <c r="G325" t="s">
         <v>1329</v>
       </c>
-    </row>
-    <row r="326" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H325" t="str">
+        <f t="shared" si="11"/>
+        <v>OriginalDisplayBcc = 0x0072,</v>
+      </c>
+    </row>
+    <row r="326" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A326" t="s">
         <v>1332</v>
       </c>
@@ -16685,6 +16975,10 @@
       <c r="C326" t="s">
         <v>1330</v>
       </c>
+      <c r="D326" t="str">
+        <f t="shared" si="10"/>
+        <v>OriginalDisplayCc</v>
+      </c>
       <c r="E326" t="s">
         <v>1331</v>
       </c>
@@ -16694,8 +16988,12 @@
       <c r="G326" t="s">
         <v>1333</v>
       </c>
-    </row>
-    <row r="327" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H326" t="str">
+        <f t="shared" si="11"/>
+        <v>OriginalDisplayCc = 0x0073,</v>
+      </c>
+    </row>
+    <row r="327" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A327" t="s">
         <v>1336</v>
       </c>
@@ -16705,6 +17003,10 @@
       <c r="C327" t="s">
         <v>1334</v>
       </c>
+      <c r="D327" t="str">
+        <f t="shared" si="10"/>
+        <v>OriginalDisplayTo</v>
+      </c>
       <c r="E327" t="s">
         <v>1335</v>
       </c>
@@ -16714,8 +17016,12 @@
       <c r="G327" t="s">
         <v>1337</v>
       </c>
-    </row>
-    <row r="328" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H327" t="str">
+        <f t="shared" si="11"/>
+        <v>OriginalDisplayTo = 0x0074,</v>
+      </c>
+    </row>
+    <row r="328" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A328" t="s">
         <v>1340</v>
       </c>
@@ -16725,6 +17031,10 @@
       <c r="C328" t="s">
         <v>1338</v>
       </c>
+      <c r="D328" t="str">
+        <f t="shared" si="10"/>
+        <v>OriginalEntryId</v>
+      </c>
       <c r="E328" t="s">
         <v>1339</v>
       </c>
@@ -16734,8 +17044,12 @@
       <c r="G328" t="s">
         <v>1341</v>
       </c>
-    </row>
-    <row r="329" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H328" t="str">
+        <f t="shared" si="11"/>
+        <v>OriginalEntryId = 0x3A12,</v>
+      </c>
+    </row>
+    <row r="329" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A329" t="s">
         <v>1344</v>
       </c>
@@ -16745,6 +17059,10 @@
       <c r="C329" t="s">
         <v>1342</v>
       </c>
+      <c r="D329" t="str">
+        <f t="shared" si="10"/>
+        <v>OriginalMessageClass</v>
+      </c>
       <c r="E329" t="s">
         <v>1343</v>
       </c>
@@ -16754,8 +17072,12 @@
       <c r="G329" t="s">
         <v>1345</v>
       </c>
-    </row>
-    <row r="330" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H329" t="str">
+        <f t="shared" si="11"/>
+        <v>OriginalMessageClass = 0x004B,</v>
+      </c>
+    </row>
+    <row r="330" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A330" t="s">
         <v>1348</v>
       </c>
@@ -16765,6 +17087,10 @@
       <c r="C330" t="s">
         <v>1346</v>
       </c>
+      <c r="D330" t="str">
+        <f t="shared" si="10"/>
+        <v>OriginalMessageId</v>
+      </c>
       <c r="E330" t="s">
         <v>1347</v>
       </c>
@@ -16774,8 +17100,12 @@
       <c r="G330" t="s">
         <v>1350</v>
       </c>
-    </row>
-    <row r="331" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H330" t="str">
+        <f t="shared" si="11"/>
+        <v>OriginalMessageId = 0x1046,</v>
+      </c>
+    </row>
+    <row r="331" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A331" t="s">
         <v>1353</v>
       </c>
@@ -16785,6 +17115,10 @@
       <c r="C331" t="s">
         <v>1351</v>
       </c>
+      <c r="D331" t="str">
+        <f t="shared" si="10"/>
+        <v>OriginalSenderAddressType</v>
+      </c>
       <c r="E331" t="s">
         <v>1352</v>
       </c>
@@ -16794,8 +17128,12 @@
       <c r="G331" t="s">
         <v>1354</v>
       </c>
-    </row>
-    <row r="332" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H331" t="str">
+        <f t="shared" si="11"/>
+        <v>OriginalSenderAddressType = 0x0066,</v>
+      </c>
+    </row>
+    <row r="332" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A332" t="s">
         <v>1357</v>
       </c>
@@ -16805,6 +17143,10 @@
       <c r="C332" t="s">
         <v>1355</v>
       </c>
+      <c r="D332" t="str">
+        <f t="shared" si="10"/>
+        <v>OriginalSenderEmailAddress</v>
+      </c>
       <c r="E332" t="s">
         <v>1356</v>
       </c>
@@ -16814,8 +17156,12 @@
       <c r="G332" t="s">
         <v>1358</v>
       </c>
-    </row>
-    <row r="333" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H332" t="str">
+        <f t="shared" si="11"/>
+        <v>OriginalSenderEmailAddress = 0x0067,</v>
+      </c>
+    </row>
+    <row r="333" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A333" t="s">
         <v>1361</v>
       </c>
@@ -16825,6 +17171,10 @@
       <c r="C333" t="s">
         <v>1359</v>
       </c>
+      <c r="D333" t="str">
+        <f t="shared" si="10"/>
+        <v>OriginalSenderEntryId</v>
+      </c>
       <c r="E333" t="s">
         <v>1360</v>
       </c>
@@ -16834,8 +17184,12 @@
       <c r="G333" t="s">
         <v>1362</v>
       </c>
-    </row>
-    <row r="334" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H333" t="str">
+        <f t="shared" si="11"/>
+        <v>OriginalSenderEntryId = 0x005B,</v>
+      </c>
+    </row>
+    <row r="334" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A334" t="s">
         <v>1365</v>
       </c>
@@ -16845,6 +17199,10 @@
       <c r="C334" t="s">
         <v>1363</v>
       </c>
+      <c r="D334" t="str">
+        <f t="shared" si="10"/>
+        <v>OriginalSenderName</v>
+      </c>
       <c r="E334" t="s">
         <v>1364</v>
       </c>
@@ -16854,8 +17212,12 @@
       <c r="G334" t="s">
         <v>1366</v>
       </c>
-    </row>
-    <row r="335" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H334" t="str">
+        <f t="shared" si="11"/>
+        <v>OriginalSenderName = 0x005A,</v>
+      </c>
+    </row>
+    <row r="335" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A335" t="s">
         <v>1369</v>
       </c>
@@ -16865,6 +17227,10 @@
       <c r="C335" t="s">
         <v>1367</v>
       </c>
+      <c r="D335" t="str">
+        <f t="shared" si="10"/>
+        <v>OriginalSenderSearchKey</v>
+      </c>
       <c r="E335" t="s">
         <v>1368</v>
       </c>
@@ -16874,8 +17240,12 @@
       <c r="G335" t="s">
         <v>1370</v>
       </c>
-    </row>
-    <row r="336" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H335" t="str">
+        <f t="shared" si="11"/>
+        <v>OriginalSenderSearchKey = 0x005C,</v>
+      </c>
+    </row>
+    <row r="336" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A336" t="s">
         <v>1373</v>
       </c>
@@ -16885,6 +17255,10 @@
       <c r="C336" t="s">
         <v>1371</v>
       </c>
+      <c r="D336" t="str">
+        <f t="shared" si="10"/>
+        <v>OriginalSensitivity</v>
+      </c>
       <c r="E336" t="s">
         <v>1372</v>
       </c>
@@ -16894,8 +17268,12 @@
       <c r="G336" t="s">
         <v>1374</v>
       </c>
-    </row>
-    <row r="337" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H336" t="str">
+        <f t="shared" si="11"/>
+        <v>OriginalSensitivity = 0x002E,</v>
+      </c>
+    </row>
+    <row r="337" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A337" t="s">
         <v>1377</v>
       </c>
@@ -16905,6 +17283,10 @@
       <c r="C337" t="s">
         <v>1375</v>
       </c>
+      <c r="D337" t="str">
+        <f t="shared" si="10"/>
+        <v>OriginalSentRepresentingAddressType</v>
+      </c>
       <c r="E337" t="s">
         <v>1376</v>
       </c>
@@ -16914,8 +17296,12 @@
       <c r="G337" t="s">
         <v>1378</v>
       </c>
-    </row>
-    <row r="338" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H337" t="str">
+        <f t="shared" si="11"/>
+        <v>OriginalSentRepresentingAddressType = 0x0068,</v>
+      </c>
+    </row>
+    <row r="338" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A338" t="s">
         <v>1381</v>
       </c>
@@ -16925,6 +17311,10 @@
       <c r="C338" t="s">
         <v>1379</v>
       </c>
+      <c r="D338" t="str">
+        <f t="shared" si="10"/>
+        <v>OriginalSentRepresentingEmailAddress</v>
+      </c>
       <c r="E338" t="s">
         <v>1380</v>
       </c>
@@ -16934,8 +17324,12 @@
       <c r="G338" t="s">
         <v>1382</v>
       </c>
-    </row>
-    <row r="339" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H338" t="str">
+        <f t="shared" si="11"/>
+        <v>OriginalSentRepresentingEmailAddress = 0x0069,</v>
+      </c>
+    </row>
+    <row r="339" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A339" t="s">
         <v>1385</v>
       </c>
@@ -16945,6 +17339,10 @@
       <c r="C339" t="s">
         <v>1383</v>
       </c>
+      <c r="D339" t="str">
+        <f t="shared" si="10"/>
+        <v>OriginalSentRepresentingEntryId</v>
+      </c>
       <c r="E339" t="s">
         <v>1384</v>
       </c>
@@ -16954,8 +17352,12 @@
       <c r="G339" t="s">
         <v>1386</v>
       </c>
-    </row>
-    <row r="340" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H339" t="str">
+        <f t="shared" si="11"/>
+        <v>OriginalSentRepresentingEntryId = 0x005E,</v>
+      </c>
+    </row>
+    <row r="340" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A340" t="s">
         <v>1389</v>
       </c>
@@ -16965,6 +17367,10 @@
       <c r="C340" t="s">
         <v>1387</v>
       </c>
+      <c r="D340" t="str">
+        <f t="shared" si="10"/>
+        <v>OriginalSentRepresentingName</v>
+      </c>
       <c r="E340" t="s">
         <v>1388</v>
       </c>
@@ -16974,8 +17380,12 @@
       <c r="G340" t="s">
         <v>1390</v>
       </c>
-    </row>
-    <row r="341" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H340" t="str">
+        <f t="shared" si="11"/>
+        <v>OriginalSentRepresentingName = 0x005D,</v>
+      </c>
+    </row>
+    <row r="341" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A341" t="s">
         <v>1393</v>
       </c>
@@ -16985,6 +17395,10 @@
       <c r="C341" t="s">
         <v>1391</v>
       </c>
+      <c r="D341" t="str">
+        <f t="shared" si="10"/>
+        <v>OriginalSentRepresentingSearchKey</v>
+      </c>
       <c r="E341" t="s">
         <v>1392</v>
       </c>
@@ -16994,8 +17408,12 @@
       <c r="G341" t="s">
         <v>1394</v>
       </c>
-    </row>
-    <row r="342" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H341" t="str">
+        <f t="shared" si="11"/>
+        <v>OriginalSentRepresentingSearchKey = 0x005F,</v>
+      </c>
+    </row>
+    <row r="342" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A342" t="s">
         <v>1397</v>
       </c>
@@ -17005,6 +17423,10 @@
       <c r="C342" t="s">
         <v>1395</v>
       </c>
+      <c r="D342" t="str">
+        <f t="shared" si="10"/>
+        <v>OriginalSubject</v>
+      </c>
       <c r="E342" t="s">
         <v>1396</v>
       </c>
@@ -17014,8 +17436,12 @@
       <c r="G342" t="s">
         <v>1398</v>
       </c>
-    </row>
-    <row r="343" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H342" t="str">
+        <f t="shared" si="11"/>
+        <v>OriginalSubject = 0x0049,</v>
+      </c>
+    </row>
+    <row r="343" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A343" t="s">
         <v>1401</v>
       </c>
@@ -17025,6 +17451,10 @@
       <c r="C343" t="s">
         <v>1399</v>
       </c>
+      <c r="D343" t="str">
+        <f t="shared" si="10"/>
+        <v>OriginalSubmitTime</v>
+      </c>
       <c r="E343" t="s">
         <v>1400</v>
       </c>
@@ -17034,8 +17464,12 @@
       <c r="G343" t="s">
         <v>1402</v>
       </c>
-    </row>
-    <row r="344" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H343" t="str">
+        <f t="shared" si="11"/>
+        <v>OriginalSubmitTime = 0x004E,</v>
+      </c>
+    </row>
+    <row r="344" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A344" t="s">
         <v>1405</v>
       </c>
@@ -17045,6 +17479,10 @@
       <c r="C344" t="s">
         <v>1403</v>
       </c>
+      <c r="D344" t="str">
+        <f t="shared" si="10"/>
+        <v>OriginatorDeliveryReportRequested</v>
+      </c>
       <c r="E344" t="s">
         <v>1404</v>
       </c>
@@ -17054,8 +17492,12 @@
       <c r="G344" t="s">
         <v>1406</v>
       </c>
-    </row>
-    <row r="345" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H344" t="str">
+        <f t="shared" si="11"/>
+        <v>OriginatorDeliveryReportRequested = 0x0023,</v>
+      </c>
+    </row>
+    <row r="345" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A345" t="s">
         <v>1409</v>
       </c>
@@ -17065,6 +17507,10 @@
       <c r="C345" t="s">
         <v>1407</v>
       </c>
+      <c r="D345" t="str">
+        <f t="shared" si="10"/>
+        <v>OriginatorNonDeliveryReportRequested</v>
+      </c>
       <c r="E345" t="s">
         <v>1408</v>
       </c>
@@ -17074,8 +17520,12 @@
       <c r="G345" t="s">
         <v>1410</v>
       </c>
-    </row>
-    <row r="346" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H345" t="str">
+        <f t="shared" si="11"/>
+        <v>OriginatorNonDeliveryReportRequested = 0x0C08,</v>
+      </c>
+    </row>
+    <row r="346" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A346" t="s">
         <v>1413</v>
       </c>
@@ -17085,6 +17535,10 @@
       <c r="C346" t="s">
         <v>1411</v>
       </c>
+      <c r="D346" t="str">
+        <f t="shared" si="10"/>
+        <v>OscSyncEnabled</v>
+      </c>
       <c r="E346" t="s">
         <v>1412</v>
       </c>
@@ -17094,8 +17548,12 @@
       <c r="G346" t="s">
         <v>1414</v>
       </c>
-    </row>
-    <row r="347" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H346" t="str">
+        <f t="shared" si="11"/>
+        <v>OscSyncEnabled = 0x7C24,</v>
+      </c>
+    </row>
+    <row r="347" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A347" t="s">
         <v>1417</v>
       </c>
@@ -17105,6 +17563,10 @@
       <c r="C347" t="s">
         <v>1415</v>
       </c>
+      <c r="D347" t="str">
+        <f t="shared" si="10"/>
+        <v>OtherAddressCity</v>
+      </c>
       <c r="E347" t="s">
         <v>1416</v>
       </c>
@@ -17114,8 +17576,12 @@
       <c r="G347" t="s">
         <v>23</v>
       </c>
-    </row>
-    <row r="348" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H347" t="str">
+        <f t="shared" si="11"/>
+        <v>OtherAddressCity = 0x3A5F,</v>
+      </c>
+    </row>
+    <row r="348" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A348" t="s">
         <v>1420</v>
       </c>
@@ -17125,6 +17591,10 @@
       <c r="C348" t="s">
         <v>1418</v>
       </c>
+      <c r="D348" t="str">
+        <f t="shared" si="10"/>
+        <v>OtherAddressCountry</v>
+      </c>
       <c r="E348" t="s">
         <v>1419</v>
       </c>
@@ -17134,8 +17604,12 @@
       <c r="G348" t="s">
         <v>24</v>
       </c>
-    </row>
-    <row r="349" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H348" t="str">
+        <f t="shared" si="11"/>
+        <v>OtherAddressCountry = 0x3A60,</v>
+      </c>
+    </row>
+    <row r="349" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A349" t="s">
         <v>1423</v>
       </c>
@@ -17145,6 +17619,10 @@
       <c r="C349" t="s">
         <v>1421</v>
       </c>
+      <c r="D349" t="str">
+        <f t="shared" si="10"/>
+        <v>OtherAddressPostalCode</v>
+      </c>
       <c r="E349" t="s">
         <v>1422</v>
       </c>
@@ -17154,8 +17632,12 @@
       <c r="G349" t="s">
         <v>25</v>
       </c>
-    </row>
-    <row r="350" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H349" t="str">
+        <f t="shared" si="11"/>
+        <v>OtherAddressPostalCode = 0x3A61,</v>
+      </c>
+    </row>
+    <row r="350" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A350" t="s">
         <v>1426</v>
       </c>
@@ -17165,6 +17647,10 @@
       <c r="C350" t="s">
         <v>1424</v>
       </c>
+      <c r="D350" t="str">
+        <f t="shared" si="10"/>
+        <v>OtherAddressPostOfficeBox</v>
+      </c>
       <c r="E350" t="s">
         <v>1425</v>
       </c>
@@ -17174,8 +17660,12 @@
       <c r="G350" t="s">
         <v>26</v>
       </c>
-    </row>
-    <row r="351" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H350" t="str">
+        <f t="shared" si="11"/>
+        <v>OtherAddressPostOfficeBox = 0x3A64,</v>
+      </c>
+    </row>
+    <row r="351" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A351" t="s">
         <v>1429</v>
       </c>
@@ -17185,6 +17675,10 @@
       <c r="C351" t="s">
         <v>1427</v>
       </c>
+      <c r="D351" t="str">
+        <f t="shared" si="10"/>
+        <v>OtherAddressStateOrProvince</v>
+      </c>
       <c r="E351" t="s">
         <v>1428</v>
       </c>
@@ -17194,8 +17688,12 @@
       <c r="G351" t="s">
         <v>27</v>
       </c>
-    </row>
-    <row r="352" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H351" t="str">
+        <f t="shared" si="11"/>
+        <v>OtherAddressStateOrProvince = 0x3A62,</v>
+      </c>
+    </row>
+    <row r="352" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A352" t="s">
         <v>1432</v>
       </c>
@@ -17205,6 +17703,10 @@
       <c r="C352" t="s">
         <v>1430</v>
       </c>
+      <c r="D352" t="str">
+        <f t="shared" si="10"/>
+        <v>OtherAddressStreet</v>
+      </c>
       <c r="E352" t="s">
         <v>1431</v>
       </c>
@@ -17214,8 +17716,12 @@
       <c r="G352" t="s">
         <v>28</v>
       </c>
-    </row>
-    <row r="353" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H352" t="str">
+        <f t="shared" si="11"/>
+        <v>OtherAddressStreet = 0x3A63,</v>
+      </c>
+    </row>
+    <row r="353" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A353" t="s">
         <v>1435</v>
       </c>
@@ -17225,6 +17731,10 @@
       <c r="C353" t="s">
         <v>1433</v>
       </c>
+      <c r="D353" t="str">
+        <f t="shared" si="10"/>
+        <v>OtherTelephoneNumber</v>
+      </c>
       <c r="E353" t="s">
         <v>1434</v>
       </c>
@@ -17234,8 +17744,12 @@
       <c r="G353" t="s">
         <v>1436</v>
       </c>
-    </row>
-    <row r="354" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H353" t="str">
+        <f t="shared" si="11"/>
+        <v>OtherTelephoneNumber = 0x3A1F,</v>
+      </c>
+    </row>
+    <row r="354" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A354" t="s">
         <v>1439</v>
       </c>
@@ -17245,6 +17759,10 @@
       <c r="C354" t="s">
         <v>1437</v>
       </c>
+      <c r="D354" t="str">
+        <f t="shared" si="10"/>
+        <v>OutOfOfficeState</v>
+      </c>
       <c r="E354" t="s">
         <v>1438</v>
       </c>
@@ -17254,8 +17772,12 @@
       <c r="G354" t="s">
         <v>1440</v>
       </c>
-    </row>
-    <row r="355" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H354" t="str">
+        <f t="shared" si="11"/>
+        <v>OutOfOfficeState = 0x661D,</v>
+      </c>
+    </row>
+    <row r="355" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A355" t="s">
         <v>1443</v>
       </c>
@@ -17265,6 +17787,10 @@
       <c r="C355" t="s">
         <v>1441</v>
       </c>
+      <c r="D355" t="str">
+        <f t="shared" si="10"/>
+        <v>OwnerAppointmentId</v>
+      </c>
       <c r="E355" t="s">
         <v>1442</v>
       </c>
@@ -17274,8 +17800,12 @@
       <c r="G355" t="s">
         <v>1445</v>
       </c>
-    </row>
-    <row r="356" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H355" t="str">
+        <f t="shared" si="11"/>
+        <v>OwnerAppointmentId = 0x0062,</v>
+      </c>
+    </row>
+    <row r="356" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A356" t="s">
         <v>1448</v>
       </c>
@@ -17285,6 +17815,10 @@
       <c r="C356" t="s">
         <v>1446</v>
       </c>
+      <c r="D356" t="str">
+        <f t="shared" si="10"/>
+        <v>PagerTelephoneNumber</v>
+      </c>
       <c r="E356" t="s">
         <v>1447</v>
       </c>
@@ -17294,8 +17828,12 @@
       <c r="G356" t="s">
         <v>1449</v>
       </c>
-    </row>
-    <row r="357" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H356" t="str">
+        <f t="shared" si="11"/>
+        <v>PagerTelephoneNumber = 0x3A21,</v>
+      </c>
+    </row>
+    <row r="357" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A357" t="s">
         <v>1452</v>
       </c>
@@ -17305,6 +17843,10 @@
       <c r="C357" t="s">
         <v>1450</v>
       </c>
+      <c r="D357" t="str">
+        <f t="shared" si="10"/>
+        <v>ParentEntryId</v>
+      </c>
       <c r="E357" t="s">
         <v>1451</v>
       </c>
@@ -17314,8 +17856,12 @@
       <c r="G357" t="s">
         <v>1453</v>
       </c>
-    </row>
-    <row r="358" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H357" t="str">
+        <f t="shared" si="11"/>
+        <v>ParentEntryId = 0x0E09,</v>
+      </c>
+    </row>
+    <row r="358" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A358" t="s">
         <v>1456</v>
       </c>
@@ -17325,6 +17871,10 @@
       <c r="C358" t="s">
         <v>1454</v>
       </c>
+      <c r="D358" t="str">
+        <f t="shared" si="10"/>
+        <v>ParentFolderId</v>
+      </c>
       <c r="E358" t="s">
         <v>1455</v>
       </c>
@@ -17334,8 +17884,12 @@
       <c r="G358" t="s">
         <v>1457</v>
       </c>
-    </row>
-    <row r="359" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H358" t="str">
+        <f t="shared" si="11"/>
+        <v>ParentFolderId = 0x6749,</v>
+      </c>
+    </row>
+    <row r="359" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A359" t="s">
         <v>1460</v>
       </c>
@@ -17345,6 +17899,10 @@
       <c r="C359" t="s">
         <v>1458</v>
       </c>
+      <c r="D359" t="str">
+        <f t="shared" si="10"/>
+        <v>ParentKey</v>
+      </c>
       <c r="E359" t="s">
         <v>1459</v>
       </c>
@@ -17354,8 +17912,12 @@
       <c r="G359" t="s">
         <v>1461</v>
       </c>
-    </row>
-    <row r="360" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H359" t="str">
+        <f t="shared" si="11"/>
+        <v>ParentKey = 0x0025,</v>
+      </c>
+    </row>
+    <row r="360" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A360" t="s">
         <v>1464</v>
       </c>
@@ -17365,6 +17927,10 @@
       <c r="C360" t="s">
         <v>1462</v>
       </c>
+      <c r="D360" t="str">
+        <f t="shared" si="10"/>
+        <v>ParentSourceKey</v>
+      </c>
       <c r="E360" t="s">
         <v>1463</v>
       </c>
@@ -17374,8 +17940,12 @@
       <c r="G360" t="s">
         <v>1466</v>
       </c>
-    </row>
-    <row r="361" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H360" t="str">
+        <f t="shared" si="11"/>
+        <v>ParentSourceKey = 0x65E1,</v>
+      </c>
+    </row>
+    <row r="361" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A361" t="s">
         <v>1469</v>
       </c>
@@ -17385,6 +17955,10 @@
       <c r="C361" t="s">
         <v>1467</v>
       </c>
+      <c r="D361" t="str">
+        <f t="shared" si="10"/>
+        <v>PersonalHomePage</v>
+      </c>
       <c r="E361" t="s">
         <v>1468</v>
       </c>
@@ -17394,8 +17968,12 @@
       <c r="G361" t="s">
         <v>1470</v>
       </c>
-    </row>
-    <row r="362" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H361" t="str">
+        <f t="shared" si="11"/>
+        <v>PersonalHomePage = 0x3A50,</v>
+      </c>
+    </row>
+    <row r="362" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A362" t="s">
         <v>1473</v>
       </c>
@@ -17405,6 +17983,10 @@
       <c r="C362" t="s">
         <v>1471</v>
       </c>
+      <c r="D362" t="str">
+        <f t="shared" si="10"/>
+        <v>PolicyTag</v>
+      </c>
       <c r="E362" t="s">
         <v>1472</v>
       </c>
@@ -17414,8 +17996,12 @@
       <c r="G362" t="s">
         <v>1474</v>
       </c>
-    </row>
-    <row r="363" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H362" t="str">
+        <f t="shared" si="11"/>
+        <v>PolicyTag = 0x3019,</v>
+      </c>
+    </row>
+    <row r="363" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A363" t="s">
         <v>1477</v>
       </c>
@@ -17425,6 +18011,10 @@
       <c r="C363" t="s">
         <v>1475</v>
       </c>
+      <c r="D363" t="str">
+        <f t="shared" si="10"/>
+        <v>PostalAddress</v>
+      </c>
       <c r="E363" t="s">
         <v>1476</v>
       </c>
@@ -17434,8 +18024,12 @@
       <c r="G363" t="s">
         <v>20</v>
       </c>
-    </row>
-    <row r="364" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H363" t="str">
+        <f t="shared" si="11"/>
+        <v>PostalAddress = 0x3A15,</v>
+      </c>
+    </row>
+    <row r="364" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A364" t="s">
         <v>1480</v>
       </c>
@@ -17445,6 +18039,10 @@
       <c r="C364" t="s">
         <v>1478</v>
       </c>
+      <c r="D364" t="str">
+        <f t="shared" si="10"/>
+        <v>PostalCode</v>
+      </c>
       <c r="E364" t="s">
         <v>1479</v>
       </c>
@@ -17454,8 +18052,12 @@
       <c r="G364" t="s">
         <v>1481</v>
       </c>
-    </row>
-    <row r="365" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H364" t="str">
+        <f t="shared" si="11"/>
+        <v>PostalCode = 0x3A2A,</v>
+      </c>
+    </row>
+    <row r="365" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A365" t="s">
         <v>1484</v>
       </c>
@@ -17465,6 +18067,10 @@
       <c r="C365" t="s">
         <v>1482</v>
       </c>
+      <c r="D365" t="str">
+        <f t="shared" si="10"/>
+        <v>PostOfficeBox</v>
+      </c>
       <c r="E365" t="s">
         <v>1483</v>
       </c>
@@ -17474,8 +18080,12 @@
       <c r="G365" t="s">
         <v>1485</v>
       </c>
-    </row>
-    <row r="366" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H365" t="str">
+        <f t="shared" si="11"/>
+        <v>PostOfficeBox = 0x3A2B,</v>
+      </c>
+    </row>
+    <row r="366" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A366" t="s">
         <v>1488</v>
       </c>
@@ -17485,6 +18095,10 @@
       <c r="C366" t="s">
         <v>1486</v>
       </c>
+      <c r="D366" t="str">
+        <f t="shared" si="10"/>
+        <v>PredecessorChangeList</v>
+      </c>
       <c r="E366" t="s">
         <v>1487</v>
       </c>
@@ -17494,8 +18108,12 @@
       <c r="G366" t="s">
         <v>1489</v>
       </c>
-    </row>
-    <row r="367" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H366" t="str">
+        <f t="shared" si="11"/>
+        <v>PredecessorChangeList = 0x65E3,</v>
+      </c>
+    </row>
+    <row r="367" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A367" t="s">
         <v>1492</v>
       </c>
@@ -17505,6 +18123,10 @@
       <c r="C367" t="s">
         <v>1490</v>
       </c>
+      <c r="D367" t="str">
+        <f t="shared" si="10"/>
+        <v>PrimaryFaxNumber</v>
+      </c>
       <c r="E367" t="s">
         <v>1491</v>
       </c>
@@ -17514,8 +18136,12 @@
       <c r="G367" t="s">
         <v>1493</v>
       </c>
-    </row>
-    <row r="368" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H367" t="str">
+        <f t="shared" si="11"/>
+        <v>PrimaryFaxNumber = 0x3A23,</v>
+      </c>
+    </row>
+    <row r="368" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A368" t="s">
         <v>1496</v>
       </c>
@@ -17525,6 +18151,10 @@
       <c r="C368" t="s">
         <v>1494</v>
       </c>
+      <c r="D368" t="str">
+        <f t="shared" si="10"/>
+        <v>PrimarySendAccount</v>
+      </c>
       <c r="E368" t="s">
         <v>1495</v>
       </c>
@@ -17534,8 +18164,12 @@
       <c r="G368" t="s">
         <v>1497</v>
       </c>
-    </row>
-    <row r="369" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H368" t="str">
+        <f t="shared" si="11"/>
+        <v>PrimarySendAccount = 0x0E28,</v>
+      </c>
+    </row>
+    <row r="369" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A369" t="s">
         <v>1500</v>
       </c>
@@ -17545,6 +18179,10 @@
       <c r="C369" t="s">
         <v>1498</v>
       </c>
+      <c r="D369" t="str">
+        <f t="shared" si="10"/>
+        <v>PrimaryTelephoneNumber</v>
+      </c>
       <c r="E369" t="s">
         <v>1499</v>
       </c>
@@ -17554,8 +18192,12 @@
       <c r="G369" t="s">
         <v>1501</v>
       </c>
-    </row>
-    <row r="370" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H369" t="str">
+        <f t="shared" si="11"/>
+        <v>PrimaryTelephoneNumber = 0x3A1A,</v>
+      </c>
+    </row>
+    <row r="370" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A370" t="s">
         <v>1504</v>
       </c>
@@ -17565,6 +18207,10 @@
       <c r="C370" t="s">
         <v>1502</v>
       </c>
+      <c r="D370" t="str">
+        <f t="shared" si="10"/>
+        <v>Priority</v>
+      </c>
       <c r="E370" t="s">
         <v>1503</v>
       </c>
@@ -17574,8 +18220,12 @@
       <c r="G370" t="s">
         <v>1505</v>
       </c>
-    </row>
-    <row r="371" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H370" t="str">
+        <f t="shared" si="11"/>
+        <v>Priority = 0x0026,</v>
+      </c>
+    </row>
+    <row r="371" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A371" t="s">
         <v>1508</v>
       </c>
@@ -17585,6 +18235,10 @@
       <c r="C371" t="s">
         <v>1506</v>
       </c>
+      <c r="D371" t="str">
+        <f t="shared" si="10"/>
+        <v>Processed</v>
+      </c>
       <c r="E371" t="s">
         <v>1507</v>
       </c>
@@ -17594,8 +18248,12 @@
       <c r="G371" t="s">
         <v>1509</v>
       </c>
-    </row>
-    <row r="372" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H371" t="str">
+        <f t="shared" si="11"/>
+        <v>Processed = 0x7D01,</v>
+      </c>
+    </row>
+    <row r="372" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A372" t="s">
         <v>1512</v>
       </c>
@@ -17605,6 +18263,10 @@
       <c r="C372" t="s">
         <v>1510</v>
       </c>
+      <c r="D372" t="str">
+        <f t="shared" si="10"/>
+        <v>Profession</v>
+      </c>
       <c r="E372" t="s">
         <v>1511</v>
       </c>
@@ -17614,8 +18276,12 @@
       <c r="G372" t="s">
         <v>1513</v>
       </c>
-    </row>
-    <row r="373" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H372" t="str">
+        <f t="shared" si="11"/>
+        <v>Profession = 0x3A46,</v>
+      </c>
+    </row>
+    <row r="373" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A373" t="s">
         <v>1516</v>
       </c>
@@ -17625,6 +18291,10 @@
       <c r="C373" t="s">
         <v>1514</v>
       </c>
+      <c r="D373" t="str">
+        <f t="shared" si="10"/>
+        <v>ProhibitReceiveQuota</v>
+      </c>
       <c r="E373" t="s">
         <v>1515</v>
       </c>
@@ -17634,8 +18304,12 @@
       <c r="G373" t="s">
         <v>1518</v>
       </c>
-    </row>
-    <row r="374" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H373" t="str">
+        <f t="shared" si="11"/>
+        <v>ProhibitReceiveQuota = 0x666A,</v>
+      </c>
+    </row>
+    <row r="374" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A374" t="s">
         <v>1521</v>
       </c>
@@ -17645,6 +18319,10 @@
       <c r="C374" t="s">
         <v>1519</v>
       </c>
+      <c r="D374" t="str">
+        <f t="shared" si="10"/>
+        <v>ProhibitSendQuota</v>
+      </c>
       <c r="E374" t="s">
         <v>1520</v>
       </c>
@@ -17654,8 +18332,12 @@
       <c r="G374" t="s">
         <v>1522</v>
       </c>
-    </row>
-    <row r="375" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H374" t="str">
+        <f t="shared" si="11"/>
+        <v>ProhibitSendQuota = 0x666E,</v>
+      </c>
+    </row>
+    <row r="375" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A375" t="s">
         <v>1525</v>
       </c>
@@ -17665,6 +18347,10 @@
       <c r="C375" t="s">
         <v>1523</v>
       </c>
+      <c r="D375" t="str">
+        <f t="shared" si="10"/>
+        <v>PurportedSenderDomain</v>
+      </c>
       <c r="E375" t="s">
         <v>1524</v>
       </c>
@@ -17674,8 +18360,12 @@
       <c r="G375" t="s">
         <v>1526</v>
       </c>
-    </row>
-    <row r="376" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H375" t="str">
+        <f t="shared" si="11"/>
+        <v>PurportedSenderDomain = 0x4083,</v>
+      </c>
+    </row>
+    <row r="376" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A376" t="s">
         <v>1529</v>
       </c>
@@ -17685,6 +18375,10 @@
       <c r="C376" t="s">
         <v>1527</v>
       </c>
+      <c r="D376" t="str">
+        <f t="shared" si="10"/>
+        <v>RadioTelephoneNumber</v>
+      </c>
       <c r="E376" t="s">
         <v>1528</v>
       </c>
@@ -17694,8 +18388,12 @@
       <c r="G376" t="s">
         <v>1530</v>
       </c>
-    </row>
-    <row r="377" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H376" t="str">
+        <f t="shared" si="11"/>
+        <v>RadioTelephoneNumber = 0x3A1D,</v>
+      </c>
+    </row>
+    <row r="377" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A377" t="s">
         <v>1533</v>
       </c>
@@ -17705,6 +18403,10 @@
       <c r="C377" t="s">
         <v>1531</v>
       </c>
+      <c r="D377" t="str">
+        <f t="shared" si="10"/>
+        <v>Read</v>
+      </c>
       <c r="E377" t="s">
         <v>1532</v>
       </c>
@@ -17714,8 +18416,12 @@
       <c r="G377" t="s">
         <v>1535</v>
       </c>
-    </row>
-    <row r="378" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H377" t="str">
+        <f t="shared" si="11"/>
+        <v>Read = 0x0E69,</v>
+      </c>
+    </row>
+    <row r="378" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A378" t="s">
         <v>1538</v>
       </c>
@@ -17725,6 +18431,10 @@
       <c r="C378" t="s">
         <v>1536</v>
       </c>
+      <c r="D378" t="str">
+        <f t="shared" si="10"/>
+        <v>ReadReceiptAddressType</v>
+      </c>
       <c r="E378" t="s">
         <v>1537</v>
       </c>
@@ -17734,8 +18444,12 @@
       <c r="G378" t="s">
         <v>1540</v>
       </c>
-    </row>
-    <row r="379" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H378" t="str">
+        <f t="shared" si="11"/>
+        <v>ReadReceiptAddressType = 0x4029,</v>
+      </c>
+    </row>
+    <row r="379" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A379" t="s">
         <v>1543</v>
       </c>
@@ -17745,6 +18459,10 @@
       <c r="C379" t="s">
         <v>1541</v>
       </c>
+      <c r="D379" t="str">
+        <f t="shared" si="10"/>
+        <v>ReadReceiptEmailAddress</v>
+      </c>
       <c r="E379" t="s">
         <v>1542</v>
       </c>
@@ -17754,8 +18472,12 @@
       <c r="G379" t="s">
         <v>1544</v>
       </c>
-    </row>
-    <row r="380" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H379" t="str">
+        <f t="shared" si="11"/>
+        <v>ReadReceiptEmailAddress = 0x402A,</v>
+      </c>
+    </row>
+    <row r="380" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A380" t="s">
         <v>1547</v>
       </c>
@@ -17765,6 +18487,10 @@
       <c r="C380" t="s">
         <v>1545</v>
       </c>
+      <c r="D380" t="str">
+        <f t="shared" si="10"/>
+        <v>ReadReceiptEntryId</v>
+      </c>
       <c r="E380" t="s">
         <v>1546</v>
       </c>
@@ -17774,8 +18500,12 @@
       <c r="G380" t="s">
         <v>1548</v>
       </c>
-    </row>
-    <row r="381" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H380" t="str">
+        <f t="shared" si="11"/>
+        <v>ReadReceiptEntryId = 0x0046,</v>
+      </c>
+    </row>
+    <row r="381" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A381" t="s">
         <v>1551</v>
       </c>
@@ -17785,6 +18515,10 @@
       <c r="C381" t="s">
         <v>1549</v>
       </c>
+      <c r="D381" t="str">
+        <f t="shared" si="10"/>
+        <v>ReadReceiptName</v>
+      </c>
       <c r="E381" t="s">
         <v>1550</v>
       </c>
@@ -17794,8 +18528,12 @@
       <c r="G381" t="s">
         <v>1552</v>
       </c>
-    </row>
-    <row r="382" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H381" t="str">
+        <f t="shared" si="11"/>
+        <v>ReadReceiptName = 0x402B,</v>
+      </c>
+    </row>
+    <row r="382" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A382" t="s">
         <v>1555</v>
       </c>
@@ -17805,6 +18543,10 @@
       <c r="C382" t="s">
         <v>1553</v>
       </c>
+      <c r="D382" t="str">
+        <f t="shared" si="10"/>
+        <v>ReadReceiptRequested</v>
+      </c>
       <c r="E382" t="s">
         <v>1554</v>
       </c>
@@ -17814,8 +18556,12 @@
       <c r="G382" t="s">
         <v>1556</v>
       </c>
-    </row>
-    <row r="383" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H382" t="str">
+        <f t="shared" si="11"/>
+        <v>ReadReceiptRequested = 0x0029,</v>
+      </c>
+    </row>
+    <row r="383" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A383" t="s">
         <v>1559</v>
       </c>
@@ -17825,6 +18571,10 @@
       <c r="C383" t="s">
         <v>1557</v>
       </c>
+      <c r="D383" t="str">
+        <f t="shared" si="10"/>
+        <v>ReadReceiptSearchKey</v>
+      </c>
       <c r="E383" t="s">
         <v>1558</v>
       </c>
@@ -17834,8 +18584,12 @@
       <c r="G383" t="s">
         <v>1560</v>
       </c>
-    </row>
-    <row r="384" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H383" t="str">
+        <f t="shared" si="11"/>
+        <v>ReadReceiptSearchKey = 0x0053,</v>
+      </c>
+    </row>
+    <row r="384" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A384" t="s">
         <v>1563</v>
       </c>
@@ -17845,6 +18599,10 @@
       <c r="C384" t="s">
         <v>1561</v>
       </c>
+      <c r="D384" t="str">
+        <f t="shared" si="10"/>
+        <v>ReadReceiptSmtpAddress</v>
+      </c>
       <c r="E384" t="s">
         <v>1562</v>
       </c>
@@ -17854,8 +18612,12 @@
       <c r="G384" t="s">
         <v>1564</v>
       </c>
-    </row>
-    <row r="385" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H384" t="str">
+        <f t="shared" si="11"/>
+        <v>ReadReceiptSmtpAddress = 0x5D05,</v>
+      </c>
+    </row>
+    <row r="385" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A385" t="s">
         <v>1567</v>
       </c>
@@ -17865,6 +18627,10 @@
       <c r="C385" t="s">
         <v>1565</v>
       </c>
+      <c r="D385" t="str">
+        <f t="shared" si="10"/>
+        <v>ReceiptTime</v>
+      </c>
       <c r="E385" t="s">
         <v>1566</v>
       </c>
@@ -17874,8 +18640,12 @@
       <c r="G385" t="s">
         <v>1568</v>
       </c>
-    </row>
-    <row r="386" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H385" t="str">
+        <f t="shared" si="11"/>
+        <v>ReceiptTime = 0x002A,</v>
+      </c>
+    </row>
+    <row r="386" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A386" t="s">
         <v>1571</v>
       </c>
@@ -17885,6 +18655,10 @@
       <c r="C386" t="s">
         <v>1569</v>
       </c>
+      <c r="D386" t="str">
+        <f t="shared" si="10"/>
+        <v>ReceivedByAddressType</v>
+      </c>
       <c r="E386" t="s">
         <v>1570</v>
       </c>
@@ -17894,8 +18668,12 @@
       <c r="G386" t="s">
         <v>1572</v>
       </c>
-    </row>
-    <row r="387" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H386" t="str">
+        <f t="shared" si="11"/>
+        <v>ReceivedByAddressType = 0x0075,</v>
+      </c>
+    </row>
+    <row r="387" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A387" t="s">
         <v>1575</v>
       </c>
@@ -17905,6 +18683,10 @@
       <c r="C387" t="s">
         <v>1573</v>
       </c>
+      <c r="D387" t="str">
+        <f t="shared" ref="D387:D450" si="12">RIGHT(C387,LEN(C387)-6)</f>
+        <v>ReceivedByEmailAddress</v>
+      </c>
       <c r="E387" t="s">
         <v>1574</v>
       </c>
@@ -17914,8 +18696,12 @@
       <c r="G387" t="s">
         <v>1576</v>
       </c>
-    </row>
-    <row r="388" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H387" t="str">
+        <f t="shared" ref="H387:H450" si="13">D387 &amp; " = " &amp; A387 &amp; ","</f>
+        <v>ReceivedByEmailAddress = 0x0076,</v>
+      </c>
+    </row>
+    <row r="388" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A388" t="s">
         <v>1579</v>
       </c>
@@ -17925,6 +18711,10 @@
       <c r="C388" t="s">
         <v>1577</v>
       </c>
+      <c r="D388" t="str">
+        <f t="shared" si="12"/>
+        <v>ReceivedByEntryId</v>
+      </c>
       <c r="E388" t="s">
         <v>1578</v>
       </c>
@@ -17934,8 +18724,12 @@
       <c r="G388" t="s">
         <v>1580</v>
       </c>
-    </row>
-    <row r="389" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H388" t="str">
+        <f t="shared" si="13"/>
+        <v>ReceivedByEntryId = 0x003F,</v>
+      </c>
+    </row>
+    <row r="389" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A389" t="s">
         <v>1583</v>
       </c>
@@ -17945,6 +18739,10 @@
       <c r="C389" t="s">
         <v>1581</v>
       </c>
+      <c r="D389" t="str">
+        <f t="shared" si="12"/>
+        <v>ReceivedByName</v>
+      </c>
       <c r="E389" t="s">
         <v>1582</v>
       </c>
@@ -17954,8 +18752,12 @@
       <c r="G389" t="s">
         <v>1584</v>
       </c>
-    </row>
-    <row r="390" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H389" t="str">
+        <f t="shared" si="13"/>
+        <v>ReceivedByName = 0x0040,</v>
+      </c>
+    </row>
+    <row r="390" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A390" t="s">
         <v>1587</v>
       </c>
@@ -17965,6 +18767,10 @@
       <c r="C390" t="s">
         <v>1585</v>
       </c>
+      <c r="D390" t="str">
+        <f t="shared" si="12"/>
+        <v>ReceivedBySearchKey</v>
+      </c>
       <c r="E390" t="s">
         <v>1586</v>
       </c>
@@ -17974,8 +18780,12 @@
       <c r="G390" t="s">
         <v>1588</v>
       </c>
-    </row>
-    <row r="391" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H390" t="str">
+        <f t="shared" si="13"/>
+        <v>ReceivedBySearchKey = 0x0051,</v>
+      </c>
+    </row>
+    <row r="391" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A391" t="s">
         <v>1591</v>
       </c>
@@ -17985,6 +18795,10 @@
       <c r="C391" t="s">
         <v>1589</v>
       </c>
+      <c r="D391" t="str">
+        <f t="shared" si="12"/>
+        <v>ReceivedBySmtpAddress</v>
+      </c>
       <c r="E391" t="s">
         <v>1590</v>
       </c>
@@ -17994,8 +18808,12 @@
       <c r="G391" t="s">
         <v>1592</v>
       </c>
-    </row>
-    <row r="392" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H391" t="str">
+        <f t="shared" si="13"/>
+        <v>ReceivedBySmtpAddress = 0x5D07,</v>
+      </c>
+    </row>
+    <row r="392" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A392" t="s">
         <v>1595</v>
       </c>
@@ -18005,6 +18823,10 @@
       <c r="C392" t="s">
         <v>1593</v>
       </c>
+      <c r="D392" t="str">
+        <f t="shared" si="12"/>
+        <v>ReceivedRepresentingAddressType</v>
+      </c>
       <c r="E392" t="s">
         <v>1594</v>
       </c>
@@ -18014,8 +18836,12 @@
       <c r="G392" t="s">
         <v>1596</v>
       </c>
-    </row>
-    <row r="393" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H392" t="str">
+        <f t="shared" si="13"/>
+        <v>ReceivedRepresentingAddressType = 0x0077,</v>
+      </c>
+    </row>
+    <row r="393" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A393" t="s">
         <v>1599</v>
       </c>
@@ -18025,6 +18851,10 @@
       <c r="C393" t="s">
         <v>1597</v>
       </c>
+      <c r="D393" t="str">
+        <f t="shared" si="12"/>
+        <v>ReceivedRepresentingEmailAddress</v>
+      </c>
       <c r="E393" t="s">
         <v>1598</v>
       </c>
@@ -18034,8 +18864,12 @@
       <c r="G393" t="s">
         <v>1600</v>
       </c>
-    </row>
-    <row r="394" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H393" t="str">
+        <f t="shared" si="13"/>
+        <v>ReceivedRepresentingEmailAddress = 0x0078,</v>
+      </c>
+    </row>
+    <row r="394" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A394" t="s">
         <v>1603</v>
       </c>
@@ -18045,6 +18879,10 @@
       <c r="C394" t="s">
         <v>1601</v>
       </c>
+      <c r="D394" t="str">
+        <f t="shared" si="12"/>
+        <v>ReceivedRepresentingEntryId</v>
+      </c>
       <c r="E394" t="s">
         <v>1602</v>
       </c>
@@ -18054,8 +18892,12 @@
       <c r="G394" t="s">
         <v>1604</v>
       </c>
-    </row>
-    <row r="395" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H394" t="str">
+        <f t="shared" si="13"/>
+        <v>ReceivedRepresentingEntryId = 0x0043,</v>
+      </c>
+    </row>
+    <row r="395" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A395" t="s">
         <v>1607</v>
       </c>
@@ -18065,6 +18907,10 @@
       <c r="C395" t="s">
         <v>1605</v>
       </c>
+      <c r="D395" t="str">
+        <f t="shared" si="12"/>
+        <v>ReceivedRepresentingName</v>
+      </c>
       <c r="E395" t="s">
         <v>1606</v>
       </c>
@@ -18074,8 +18920,12 @@
       <c r="G395" t="s">
         <v>1608</v>
       </c>
-    </row>
-    <row r="396" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H395" t="str">
+        <f t="shared" si="13"/>
+        <v>ReceivedRepresentingName = 0x0044,</v>
+      </c>
+    </row>
+    <row r="396" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A396" t="s">
         <v>1611</v>
       </c>
@@ -18085,6 +18935,10 @@
       <c r="C396" t="s">
         <v>1609</v>
       </c>
+      <c r="D396" t="str">
+        <f t="shared" si="12"/>
+        <v>ReceivedRepresentingSearchKey</v>
+      </c>
       <c r="E396" t="s">
         <v>1610</v>
       </c>
@@ -18094,8 +18948,12 @@
       <c r="G396" t="s">
         <v>1612</v>
       </c>
-    </row>
-    <row r="397" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H396" t="str">
+        <f t="shared" si="13"/>
+        <v>ReceivedRepresentingSearchKey = 0x0052,</v>
+      </c>
+    </row>
+    <row r="397" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A397" t="s">
         <v>1615</v>
       </c>
@@ -18105,6 +18963,10 @@
       <c r="C397" t="s">
         <v>1613</v>
       </c>
+      <c r="D397" t="str">
+        <f t="shared" si="12"/>
+        <v>ReceivedRepresentingSmtpAddress</v>
+      </c>
       <c r="E397" t="s">
         <v>1614</v>
       </c>
@@ -18114,8 +18976,12 @@
       <c r="G397" t="s">
         <v>1616</v>
       </c>
-    </row>
-    <row r="398" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H397" t="str">
+        <f t="shared" si="13"/>
+        <v>ReceivedRepresentingSmtpAddress = 0x5D08,</v>
+      </c>
+    </row>
+    <row r="398" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A398" t="s">
         <v>1619</v>
       </c>
@@ -18125,6 +18991,10 @@
       <c r="C398" t="s">
         <v>1617</v>
       </c>
+      <c r="D398" t="str">
+        <f t="shared" si="12"/>
+        <v>RecipientDisplayName</v>
+      </c>
       <c r="E398" t="s">
         <v>1618</v>
       </c>
@@ -18134,8 +19004,12 @@
       <c r="G398" t="s">
         <v>1621</v>
       </c>
-    </row>
-    <row r="399" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H398" t="str">
+        <f t="shared" si="13"/>
+        <v>RecipientDisplayName = 0x5FF6,</v>
+      </c>
+    </row>
+    <row r="399" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A399" t="s">
         <v>1624</v>
       </c>
@@ -18145,6 +19019,10 @@
       <c r="C399" t="s">
         <v>1622</v>
       </c>
+      <c r="D399" t="str">
+        <f t="shared" si="12"/>
+        <v>RecipientEntryId</v>
+      </c>
       <c r="E399" t="s">
         <v>1623</v>
       </c>
@@ -18154,8 +19032,12 @@
       <c r="G399" t="s">
         <v>1625</v>
       </c>
-    </row>
-    <row r="400" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H399" t="str">
+        <f t="shared" si="13"/>
+        <v>RecipientEntryId = 0x5FF7,</v>
+      </c>
+    </row>
+    <row r="400" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A400" t="s">
         <v>1628</v>
       </c>
@@ -18165,6 +19047,10 @@
       <c r="C400" t="s">
         <v>1626</v>
       </c>
+      <c r="D400" t="str">
+        <f t="shared" si="12"/>
+        <v>RecipientFlags</v>
+      </c>
       <c r="E400" t="s">
         <v>1627</v>
       </c>
@@ -18174,8 +19060,12 @@
       <c r="G400" t="s">
         <v>1629</v>
       </c>
-    </row>
-    <row r="401" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H400" t="str">
+        <f t="shared" si="13"/>
+        <v>RecipientFlags = 0x5FFD,</v>
+      </c>
+    </row>
+    <row r="401" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A401" t="s">
         <v>1632</v>
       </c>
@@ -18185,6 +19075,10 @@
       <c r="C401" t="s">
         <v>1630</v>
       </c>
+      <c r="D401" t="str">
+        <f t="shared" si="12"/>
+        <v>RecipientOrder</v>
+      </c>
       <c r="E401" t="s">
         <v>1631</v>
       </c>
@@ -18194,8 +19088,12 @@
       <c r="G401" t="s">
         <v>1633</v>
       </c>
-    </row>
-    <row r="402" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H401" t="str">
+        <f t="shared" si="13"/>
+        <v>RecipientOrder = 0x5FDF,</v>
+      </c>
+    </row>
+    <row r="402" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A402" t="s">
         <v>1636</v>
       </c>
@@ -18205,6 +19103,10 @@
       <c r="C402" t="s">
         <v>1634</v>
       </c>
+      <c r="D402" t="str">
+        <f t="shared" si="12"/>
+        <v>RecipientProposed</v>
+      </c>
       <c r="E402" t="s">
         <v>1635</v>
       </c>
@@ -18214,8 +19116,12 @@
       <c r="G402" t="s">
         <v>1637</v>
       </c>
-    </row>
-    <row r="403" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H402" t="str">
+        <f t="shared" si="13"/>
+        <v>RecipientProposed = 0x5FE1,</v>
+      </c>
+    </row>
+    <row r="403" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A403" t="s">
         <v>1640</v>
       </c>
@@ -18225,6 +19131,10 @@
       <c r="C403" t="s">
         <v>1638</v>
       </c>
+      <c r="D403" t="str">
+        <f t="shared" si="12"/>
+        <v>RecipientProposedEndTime</v>
+      </c>
       <c r="E403" t="s">
         <v>1639</v>
       </c>
@@ -18234,8 +19144,12 @@
       <c r="G403" t="s">
         <v>1641</v>
       </c>
-    </row>
-    <row r="404" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H403" t="str">
+        <f t="shared" si="13"/>
+        <v>RecipientProposedEndTime = 0x5FE4,</v>
+      </c>
+    </row>
+    <row r="404" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A404" t="s">
         <v>1644</v>
       </c>
@@ -18245,6 +19159,10 @@
       <c r="C404" t="s">
         <v>1642</v>
       </c>
+      <c r="D404" t="str">
+        <f t="shared" si="12"/>
+        <v>RecipientProposedStartTime</v>
+      </c>
       <c r="E404" t="s">
         <v>1643</v>
       </c>
@@ -18254,8 +19172,12 @@
       <c r="G404" t="s">
         <v>1645</v>
       </c>
-    </row>
-    <row r="405" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H404" t="str">
+        <f t="shared" si="13"/>
+        <v>RecipientProposedStartTime = 0x5FE3,</v>
+      </c>
+    </row>
+    <row r="405" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A405" t="s">
         <v>1648</v>
       </c>
@@ -18265,6 +19187,10 @@
       <c r="C405" t="s">
         <v>1646</v>
       </c>
+      <c r="D405" t="str">
+        <f t="shared" si="12"/>
+        <v>RecipientReassignmentProhibited</v>
+      </c>
       <c r="E405" t="s">
         <v>1647</v>
       </c>
@@ -18274,8 +19200,12 @@
       <c r="G405" t="s">
         <v>1649</v>
       </c>
-    </row>
-    <row r="406" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H405" t="str">
+        <f t="shared" si="13"/>
+        <v>RecipientReassignmentProhibited = 0x002B,</v>
+      </c>
+    </row>
+    <row r="406" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A406" t="s">
         <v>1652</v>
       </c>
@@ -18285,6 +19215,10 @@
       <c r="C406" t="s">
         <v>1650</v>
       </c>
+      <c r="D406" t="str">
+        <f t="shared" si="12"/>
+        <v>RecipientTrackStatus</v>
+      </c>
       <c r="E406" t="s">
         <v>1651</v>
       </c>
@@ -18294,8 +19228,12 @@
       <c r="G406" t="s">
         <v>1653</v>
       </c>
-    </row>
-    <row r="407" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H406" t="str">
+        <f t="shared" si="13"/>
+        <v>RecipientTrackStatus = 0x5FFF,</v>
+      </c>
+    </row>
+    <row r="407" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A407" t="s">
         <v>1656</v>
       </c>
@@ -18305,6 +19243,10 @@
       <c r="C407" t="s">
         <v>1654</v>
       </c>
+      <c r="D407" t="str">
+        <f t="shared" si="12"/>
+        <v>RecipientTrackStatusTime</v>
+      </c>
       <c r="E407" t="s">
         <v>1655</v>
       </c>
@@ -18314,8 +19256,12 @@
       <c r="G407" t="s">
         <v>1657</v>
       </c>
-    </row>
-    <row r="408" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H407" t="str">
+        <f t="shared" si="13"/>
+        <v>RecipientTrackStatusTime = 0x5FFB,</v>
+      </c>
+    </row>
+    <row r="408" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A408" t="s">
         <v>1660</v>
       </c>
@@ -18325,6 +19271,10 @@
       <c r="C408" t="s">
         <v>1658</v>
       </c>
+      <c r="D408" t="str">
+        <f t="shared" si="12"/>
+        <v>RecipientType</v>
+      </c>
       <c r="E408" t="s">
         <v>1659</v>
       </c>
@@ -18334,8 +19284,12 @@
       <c r="G408" t="s">
         <v>1662</v>
       </c>
-    </row>
-    <row r="409" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H408" t="str">
+        <f t="shared" si="13"/>
+        <v>RecipientType = 0x0C15,</v>
+      </c>
+    </row>
+    <row r="409" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A409" t="s">
         <v>1665</v>
       </c>
@@ -18345,6 +19299,10 @@
       <c r="C409" t="s">
         <v>1663</v>
       </c>
+      <c r="D409" t="str">
+        <f t="shared" si="12"/>
+        <v>RecordKey</v>
+      </c>
       <c r="E409" t="s">
         <v>1664</v>
       </c>
@@ -18354,8 +19312,12 @@
       <c r="G409" t="s">
         <v>1666</v>
       </c>
-    </row>
-    <row r="410" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H409" t="str">
+        <f t="shared" si="13"/>
+        <v>RecordKey = 0x0FF9,</v>
+      </c>
+    </row>
+    <row r="410" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A410" t="s">
         <v>1669</v>
       </c>
@@ -18365,6 +19327,10 @@
       <c r="C410" t="s">
         <v>1667</v>
       </c>
+      <c r="D410" t="str">
+        <f t="shared" si="12"/>
+        <v>ReferredByName</v>
+      </c>
       <c r="E410" t="s">
         <v>1668</v>
       </c>
@@ -18374,8 +19340,12 @@
       <c r="G410" t="s">
         <v>1670</v>
       </c>
-    </row>
-    <row r="411" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H410" t="str">
+        <f t="shared" si="13"/>
+        <v>ReferredByName = 0x3A47,</v>
+      </c>
+    </row>
+    <row r="411" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A411" t="s">
         <v>1673</v>
       </c>
@@ -18385,6 +19355,10 @@
       <c r="C411" t="s">
         <v>1671</v>
       </c>
+      <c r="D411" t="str">
+        <f t="shared" si="12"/>
+        <v>RemindersOnlineEntryId</v>
+      </c>
       <c r="E411" t="s">
         <v>1672</v>
       </c>
@@ -18394,8 +19368,12 @@
       <c r="G411" t="s">
         <v>1028</v>
       </c>
-    </row>
-    <row r="412" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H411" t="str">
+        <f t="shared" si="13"/>
+        <v>RemindersOnlineEntryId = 0x36D5,</v>
+      </c>
+    </row>
+    <row r="412" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A412" t="s">
         <v>1676</v>
       </c>
@@ -18405,6 +19383,10 @@
       <c r="C412" t="s">
         <v>1674</v>
       </c>
+      <c r="D412" t="str">
+        <f t="shared" si="12"/>
+        <v>RemoteMessageTransferAgent</v>
+      </c>
       <c r="E412" t="s">
         <v>1675</v>
       </c>
@@ -18414,8 +19396,12 @@
       <c r="G412" t="s">
         <v>1677</v>
       </c>
-    </row>
-    <row r="413" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H412" t="str">
+        <f t="shared" si="13"/>
+        <v>RemoteMessageTransferAgent = 0x0C21,</v>
+      </c>
+    </row>
+    <row r="413" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A413" t="s">
         <v>1680</v>
       </c>
@@ -18425,6 +19411,10 @@
       <c r="C413" t="s">
         <v>1678</v>
       </c>
+      <c r="D413" t="str">
+        <f t="shared" si="12"/>
+        <v>RenderingPosition</v>
+      </c>
       <c r="E413" t="s">
         <v>1679</v>
       </c>
@@ -18434,8 +19424,12 @@
       <c r="G413" t="s">
         <v>1682</v>
       </c>
-    </row>
-    <row r="414" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H413" t="str">
+        <f t="shared" si="13"/>
+        <v>RenderingPosition = 0x370B,</v>
+      </c>
+    </row>
+    <row r="414" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A414" t="s">
         <v>1685</v>
       </c>
@@ -18445,6 +19439,10 @@
       <c r="C414" t="s">
         <v>1683</v>
       </c>
+      <c r="D414" t="str">
+        <f t="shared" si="12"/>
+        <v>ReplyRecipientEntries</v>
+      </c>
       <c r="E414" t="s">
         <v>1684</v>
       </c>
@@ -18454,8 +19452,12 @@
       <c r="G414" t="s">
         <v>1686</v>
       </c>
-    </row>
-    <row r="415" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H414" t="str">
+        <f t="shared" si="13"/>
+        <v>ReplyRecipientEntries = 0x004F,</v>
+      </c>
+    </row>
+    <row r="415" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A415" t="s">
         <v>1689</v>
       </c>
@@ -18465,6 +19467,10 @@
       <c r="C415" t="s">
         <v>1687</v>
       </c>
+      <c r="D415" t="str">
+        <f t="shared" si="12"/>
+        <v>ReplyRecipientNames</v>
+      </c>
       <c r="E415" t="s">
         <v>1688</v>
       </c>
@@ -18474,8 +19480,12 @@
       <c r="G415" t="s">
         <v>1690</v>
       </c>
-    </row>
-    <row r="416" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H415" t="str">
+        <f t="shared" si="13"/>
+        <v>ReplyRecipientNames = 0x0050,</v>
+      </c>
+    </row>
+    <row r="416" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A416" t="s">
         <v>1693</v>
       </c>
@@ -18485,6 +19495,10 @@
       <c r="C416" t="s">
         <v>1691</v>
       </c>
+      <c r="D416" t="str">
+        <f t="shared" si="12"/>
+        <v>ReplyRequested</v>
+      </c>
       <c r="E416" t="s">
         <v>1692</v>
       </c>
@@ -18494,8 +19508,12 @@
       <c r="G416" t="s">
         <v>1694</v>
       </c>
-    </row>
-    <row r="417" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H416" t="str">
+        <f t="shared" si="13"/>
+        <v>ReplyRequested = 0x0C17,</v>
+      </c>
+    </row>
+    <row r="417" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A417" t="s">
         <v>1697</v>
       </c>
@@ -18505,6 +19523,10 @@
       <c r="C417" t="s">
         <v>1695</v>
       </c>
+      <c r="D417" t="str">
+        <f t="shared" si="12"/>
+        <v>ReplyTemplateId</v>
+      </c>
       <c r="E417" t="s">
         <v>1696</v>
       </c>
@@ -18514,8 +19536,12 @@
       <c r="G417" t="s">
         <v>1698</v>
       </c>
-    </row>
-    <row r="418" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H417" t="str">
+        <f t="shared" si="13"/>
+        <v>ReplyTemplateId = 0x65C2,</v>
+      </c>
+    </row>
+    <row r="418" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A418" t="s">
         <v>1701</v>
       </c>
@@ -18525,6 +19551,10 @@
       <c r="C418" t="s">
         <v>1699</v>
       </c>
+      <c r="D418" t="str">
+        <f t="shared" si="12"/>
+        <v>ReplyTime</v>
+      </c>
       <c r="E418" t="s">
         <v>1700</v>
       </c>
@@ -18534,8 +19564,12 @@
       <c r="G418" t="s">
         <v>1702</v>
       </c>
-    </row>
-    <row r="419" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H418" t="str">
+        <f t="shared" si="13"/>
+        <v>ReplyTime = 0x0030,</v>
+      </c>
+    </row>
+    <row r="419" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A419" t="s">
         <v>1705</v>
       </c>
@@ -18545,6 +19579,10 @@
       <c r="C419" t="s">
         <v>1703</v>
       </c>
+      <c r="D419" t="str">
+        <f t="shared" si="12"/>
+        <v>ReportDisposition</v>
+      </c>
       <c r="E419" t="s">
         <v>1704</v>
       </c>
@@ -18554,8 +19592,12 @@
       <c r="G419" t="s">
         <v>1706</v>
       </c>
-    </row>
-    <row r="420" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H419" t="str">
+        <f t="shared" si="13"/>
+        <v>ReportDisposition = 0x0080,</v>
+      </c>
+    </row>
+    <row r="420" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A420" t="s">
         <v>1709</v>
       </c>
@@ -18565,6 +19607,10 @@
       <c r="C420" t="s">
         <v>1707</v>
       </c>
+      <c r="D420" t="str">
+        <f t="shared" si="12"/>
+        <v>ReportDispositionMode</v>
+      </c>
       <c r="E420" t="s">
         <v>1708</v>
       </c>
@@ -18574,8 +19620,12 @@
       <c r="G420" t="s">
         <v>1710</v>
       </c>
-    </row>
-    <row r="421" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H420" t="str">
+        <f t="shared" si="13"/>
+        <v>ReportDispositionMode = 0x0081,</v>
+      </c>
+    </row>
+    <row r="421" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A421" t="s">
         <v>1713</v>
       </c>
@@ -18585,6 +19635,10 @@
       <c r="C421" t="s">
         <v>1711</v>
       </c>
+      <c r="D421" t="str">
+        <f t="shared" si="12"/>
+        <v>ReportEntryId</v>
+      </c>
       <c r="E421" t="s">
         <v>1712</v>
       </c>
@@ -18594,8 +19648,12 @@
       <c r="G421" t="s">
         <v>1694</v>
       </c>
-    </row>
-    <row r="422" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H421" t="str">
+        <f t="shared" si="13"/>
+        <v>ReportEntryId = 0x0045,</v>
+      </c>
+    </row>
+    <row r="422" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A422" t="s">
         <v>1716</v>
       </c>
@@ -18605,6 +19663,10 @@
       <c r="C422" t="s">
         <v>1714</v>
       </c>
+      <c r="D422" t="str">
+        <f t="shared" si="12"/>
+        <v>ReportingMessageTransferAgent</v>
+      </c>
       <c r="E422" t="s">
         <v>1715</v>
       </c>
@@ -18614,8 +19676,12 @@
       <c r="G422" t="s">
         <v>1717</v>
       </c>
-    </row>
-    <row r="423" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H422" t="str">
+        <f t="shared" si="13"/>
+        <v>ReportingMessageTransferAgent = 0x6820,</v>
+      </c>
+    </row>
+    <row r="423" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A423" t="s">
         <v>1720</v>
       </c>
@@ -18625,6 +19691,10 @@
       <c r="C423" t="s">
         <v>1718</v>
       </c>
+      <c r="D423" t="str">
+        <f t="shared" si="12"/>
+        <v>ReportName</v>
+      </c>
       <c r="E423" t="s">
         <v>1719</v>
       </c>
@@ -18634,8 +19704,12 @@
       <c r="G423" t="s">
         <v>1721</v>
       </c>
-    </row>
-    <row r="424" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H423" t="str">
+        <f t="shared" si="13"/>
+        <v>ReportName = 0x003A,</v>
+      </c>
+    </row>
+    <row r="424" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A424" t="s">
         <v>1724</v>
       </c>
@@ -18645,6 +19719,10 @@
       <c r="C424" t="s">
         <v>1722</v>
       </c>
+      <c r="D424" t="str">
+        <f t="shared" si="12"/>
+        <v>ReportSearchKey</v>
+      </c>
       <c r="E424" t="s">
         <v>1723</v>
       </c>
@@ -18654,8 +19732,12 @@
       <c r="G424" t="s">
         <v>1725</v>
       </c>
-    </row>
-    <row r="425" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H424" t="str">
+        <f t="shared" si="13"/>
+        <v>ReportSearchKey = 0x0054,</v>
+      </c>
+    </row>
+    <row r="425" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A425" t="s">
         <v>1728</v>
       </c>
@@ -18665,6 +19747,10 @@
       <c r="C425" t="s">
         <v>1726</v>
       </c>
+      <c r="D425" t="str">
+        <f t="shared" si="12"/>
+        <v>ReportTag</v>
+      </c>
       <c r="E425" t="s">
         <v>1727</v>
       </c>
@@ -18674,8 +19760,12 @@
       <c r="G425" t="s">
         <v>1729</v>
       </c>
-    </row>
-    <row r="426" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H425" t="str">
+        <f t="shared" si="13"/>
+        <v>ReportTag = 0x0031,</v>
+      </c>
+    </row>
+    <row r="426" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A426" t="s">
         <v>1732</v>
       </c>
@@ -18685,6 +19775,10 @@
       <c r="C426" t="s">
         <v>1730</v>
       </c>
+      <c r="D426" t="str">
+        <f t="shared" si="12"/>
+        <v>ReportText</v>
+      </c>
       <c r="E426" t="s">
         <v>1731</v>
       </c>
@@ -18694,8 +19788,12 @@
       <c r="G426" t="s">
         <v>1734</v>
       </c>
-    </row>
-    <row r="427" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H426" t="str">
+        <f t="shared" si="13"/>
+        <v>ReportText = 0x1001,</v>
+      </c>
+    </row>
+    <row r="427" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A427" t="s">
         <v>1737</v>
       </c>
@@ -18705,6 +19803,10 @@
       <c r="C427" t="s">
         <v>1735</v>
       </c>
+      <c r="D427" t="str">
+        <f t="shared" si="12"/>
+        <v>ReportTime</v>
+      </c>
       <c r="E427" t="s">
         <v>1736</v>
       </c>
@@ -18714,8 +19816,12 @@
       <c r="G427" t="s">
         <v>1738</v>
       </c>
-    </row>
-    <row r="428" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H427" t="str">
+        <f t="shared" si="13"/>
+        <v>ReportTime = 0x0032,</v>
+      </c>
+    </row>
+    <row r="428" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A428" t="s">
         <v>1741</v>
       </c>
@@ -18725,6 +19831,10 @@
       <c r="C428" t="s">
         <v>1739</v>
       </c>
+      <c r="D428" t="str">
+        <f t="shared" si="12"/>
+        <v>ResolveMethod</v>
+      </c>
       <c r="E428" t="s">
         <v>1740</v>
       </c>
@@ -18734,8 +19844,12 @@
       <c r="G428" t="s">
         <v>1742</v>
       </c>
-    </row>
-    <row r="429" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H428" t="str">
+        <f t="shared" si="13"/>
+        <v>ResolveMethod = 0x3FE7,</v>
+      </c>
+    </row>
+    <row r="429" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A429" t="s">
         <v>1745</v>
       </c>
@@ -18745,6 +19859,10 @@
       <c r="C429" t="s">
         <v>1743</v>
       </c>
+      <c r="D429" t="str">
+        <f t="shared" si="12"/>
+        <v>ResponseRequested</v>
+      </c>
       <c r="E429" t="s">
         <v>1744</v>
       </c>
@@ -18754,8 +19872,12 @@
       <c r="G429" t="s">
         <v>1746</v>
       </c>
-    </row>
-    <row r="430" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H429" t="str">
+        <f t="shared" si="13"/>
+        <v>ResponseRequested = 0x0063,</v>
+      </c>
+    </row>
+    <row r="430" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A430" t="s">
         <v>1749</v>
       </c>
@@ -18765,6 +19887,10 @@
       <c r="C430" t="s">
         <v>1747</v>
       </c>
+      <c r="D430" t="str">
+        <f t="shared" si="12"/>
+        <v>Responsibility</v>
+      </c>
       <c r="E430" t="s">
         <v>1748</v>
       </c>
@@ -18774,8 +19900,12 @@
       <c r="G430" t="s">
         <v>1750</v>
       </c>
-    </row>
-    <row r="431" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H430" t="str">
+        <f t="shared" si="13"/>
+        <v>Responsibility = 0x0E0F,</v>
+      </c>
+    </row>
+    <row r="431" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A431" t="s">
         <v>1753</v>
       </c>
@@ -18785,6 +19915,10 @@
       <c r="C431" t="s">
         <v>1751</v>
       </c>
+      <c r="D431" t="str">
+        <f t="shared" si="12"/>
+        <v>RetentionDate</v>
+      </c>
       <c r="E431" t="s">
         <v>1752</v>
       </c>
@@ -18794,8 +19928,12 @@
       <c r="G431" t="s">
         <v>1754</v>
       </c>
-    </row>
-    <row r="432" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H431" t="str">
+        <f t="shared" si="13"/>
+        <v>RetentionDate = 0x301C,</v>
+      </c>
+    </row>
+    <row r="432" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A432" t="s">
         <v>1757</v>
       </c>
@@ -18805,6 +19943,10 @@
       <c r="C432" t="s">
         <v>1755</v>
       </c>
+      <c r="D432" t="str">
+        <f t="shared" si="12"/>
+        <v>RetentionFlags</v>
+      </c>
       <c r="E432" t="s">
         <v>1756</v>
       </c>
@@ -18814,8 +19956,12 @@
       <c r="G432" t="s">
         <v>1758</v>
       </c>
-    </row>
-    <row r="433" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H432" t="str">
+        <f t="shared" si="13"/>
+        <v>RetentionFlags = 0x301D,</v>
+      </c>
+    </row>
+    <row r="433" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A433" t="s">
         <v>1760</v>
       </c>
@@ -18825,6 +19971,10 @@
       <c r="C433" t="s">
         <v>1759</v>
       </c>
+      <c r="D433" t="str">
+        <f t="shared" si="12"/>
+        <v>RetentionPeriod</v>
+      </c>
       <c r="E433" t="s">
         <v>319</v>
       </c>
@@ -18834,8 +19984,12 @@
       <c r="G433" t="s">
         <v>1761</v>
       </c>
-    </row>
-    <row r="434" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H433" t="str">
+        <f t="shared" si="13"/>
+        <v>RetentionPeriod = 0x301A,</v>
+      </c>
+    </row>
+    <row r="434" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A434" t="s">
         <v>1764</v>
       </c>
@@ -18845,6 +19999,10 @@
       <c r="C434" t="s">
         <v>1762</v>
       </c>
+      <c r="D434" t="str">
+        <f t="shared" si="12"/>
+        <v>Rights</v>
+      </c>
       <c r="E434" t="s">
         <v>1763</v>
       </c>
@@ -18854,8 +20012,12 @@
       <c r="G434" t="s">
         <v>1765</v>
       </c>
-    </row>
-    <row r="435" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H434" t="str">
+        <f t="shared" si="13"/>
+        <v>Rights = 0x6639,</v>
+      </c>
+    </row>
+    <row r="435" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A435" t="s">
         <v>1768</v>
       </c>
@@ -18865,6 +20027,10 @@
       <c r="C435" t="s">
         <v>1766</v>
       </c>
+      <c r="D435" t="str">
+        <f t="shared" si="12"/>
+        <v>RoamingDatatypes</v>
+      </c>
       <c r="E435" t="s">
         <v>1767</v>
       </c>
@@ -18874,8 +20040,12 @@
       <c r="G435" t="s">
         <v>1770</v>
       </c>
-    </row>
-    <row r="436" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H435" t="str">
+        <f t="shared" si="13"/>
+        <v>RoamingDatatypes = 0x7C06,</v>
+      </c>
+    </row>
+    <row r="436" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A436" t="s">
         <v>1773</v>
       </c>
@@ -18885,6 +20055,10 @@
       <c r="C436" t="s">
         <v>1771</v>
       </c>
+      <c r="D436" t="str">
+        <f t="shared" si="12"/>
+        <v>RoamingDictionary</v>
+      </c>
       <c r="E436" t="s">
         <v>1772</v>
       </c>
@@ -18894,8 +20068,12 @@
       <c r="G436" t="s">
         <v>1774</v>
       </c>
-    </row>
-    <row r="437" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H436" t="str">
+        <f t="shared" si="13"/>
+        <v>RoamingDictionary = 0x7C07,</v>
+      </c>
+    </row>
+    <row r="437" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A437" t="s">
         <v>1777</v>
       </c>
@@ -18905,6 +20083,10 @@
       <c r="C437" t="s">
         <v>1775</v>
       </c>
+      <c r="D437" t="str">
+        <f t="shared" si="12"/>
+        <v>RoamingXmlStream</v>
+      </c>
       <c r="E437" t="s">
         <v>1776</v>
       </c>
@@ -18914,8 +20096,12 @@
       <c r="G437" t="s">
         <v>1778</v>
       </c>
-    </row>
-    <row r="438" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H437" t="str">
+        <f t="shared" si="13"/>
+        <v>RoamingXmlStream = 0x7C08,</v>
+      </c>
+    </row>
+    <row r="438" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A438" t="s">
         <v>1781</v>
       </c>
@@ -18925,6 +20111,10 @@
       <c r="C438" t="s">
         <v>1779</v>
       </c>
+      <c r="D438" t="str">
+        <f t="shared" si="12"/>
+        <v>Rowid</v>
+      </c>
       <c r="E438" t="s">
         <v>1780</v>
       </c>
@@ -18934,8 +20124,12 @@
       <c r="G438" t="s">
         <v>1782</v>
       </c>
-    </row>
-    <row r="439" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H438" t="str">
+        <f t="shared" si="13"/>
+        <v>Rowid = 0x3000,</v>
+      </c>
+    </row>
+    <row r="439" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A439" t="s">
         <v>1785</v>
       </c>
@@ -18945,6 +20139,10 @@
       <c r="C439" t="s">
         <v>1783</v>
       </c>
+      <c r="D439" t="str">
+        <f t="shared" si="12"/>
+        <v>RowType</v>
+      </c>
       <c r="E439" t="s">
         <v>1784</v>
       </c>
@@ -18954,8 +20152,12 @@
       <c r="G439" t="s">
         <v>1786</v>
       </c>
-    </row>
-    <row r="440" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H439" t="str">
+        <f t="shared" si="13"/>
+        <v>RowType = 0x0FF5,</v>
+      </c>
+    </row>
+    <row r="440" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A440" t="s">
         <v>1789</v>
       </c>
@@ -18965,6 +20167,10 @@
       <c r="C440" t="s">
         <v>1787</v>
       </c>
+      <c r="D440" t="str">
+        <f t="shared" si="12"/>
+        <v>RtfCompressed</v>
+      </c>
       <c r="E440" t="s">
         <v>1788</v>
       </c>
@@ -18974,8 +20180,12 @@
       <c r="G440" t="s">
         <v>1790</v>
       </c>
-    </row>
-    <row r="441" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H440" t="str">
+        <f t="shared" si="13"/>
+        <v>RtfCompressed = 0x1009,</v>
+      </c>
+    </row>
+    <row r="441" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A441" t="s">
         <v>1793</v>
       </c>
@@ -18985,6 +20195,10 @@
       <c r="C441" t="s">
         <v>1791</v>
       </c>
+      <c r="D441" t="str">
+        <f t="shared" si="12"/>
+        <v>RtfInSync</v>
+      </c>
       <c r="E441" t="s">
         <v>1792</v>
       </c>
@@ -18994,8 +20208,12 @@
       <c r="G441" t="s">
         <v>1794</v>
       </c>
-    </row>
-    <row r="442" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H441" t="str">
+        <f t="shared" si="13"/>
+        <v>RtfInSync = 0x0E1F,</v>
+      </c>
+    </row>
+    <row r="442" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A442" t="s">
         <v>1797</v>
       </c>
@@ -19005,6 +20223,10 @@
       <c r="C442" t="s">
         <v>1795</v>
       </c>
+      <c r="D442" t="str">
+        <f t="shared" si="12"/>
+        <v>RuleActionNumber</v>
+      </c>
       <c r="E442" t="s">
         <v>1796</v>
       </c>
@@ -19014,8 +20236,12 @@
       <c r="G442" t="s">
         <v>1798</v>
       </c>
-    </row>
-    <row r="443" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H442" t="str">
+        <f t="shared" si="13"/>
+        <v>RuleActionNumber = 0x6650,</v>
+      </c>
+    </row>
+    <row r="443" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A443" t="s">
         <v>1801</v>
       </c>
@@ -19025,6 +20251,10 @@
       <c r="C443" t="s">
         <v>1799</v>
       </c>
+      <c r="D443" t="str">
+        <f t="shared" si="12"/>
+        <v>RuleActions</v>
+      </c>
       <c r="E443" t="s">
         <v>1800</v>
       </c>
@@ -19034,8 +20264,12 @@
       <c r="G443" t="s">
         <v>1804</v>
       </c>
-    </row>
-    <row r="444" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H443" t="str">
+        <f t="shared" si="13"/>
+        <v>RuleActions = 0x6680,</v>
+      </c>
+    </row>
+    <row r="444" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A444" t="s">
         <v>1807</v>
       </c>
@@ -19045,6 +20279,10 @@
       <c r="C444" t="s">
         <v>1805</v>
       </c>
+      <c r="D444" t="str">
+        <f t="shared" si="12"/>
+        <v>RuleActionType</v>
+      </c>
       <c r="E444" t="s">
         <v>1806</v>
       </c>
@@ -19054,8 +20292,12 @@
       <c r="G444" t="s">
         <v>1808</v>
       </c>
-    </row>
-    <row r="445" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H444" t="str">
+        <f t="shared" si="13"/>
+        <v>RuleActionType = 0x6649,</v>
+      </c>
+    </row>
+    <row r="445" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A445" t="s">
         <v>1811</v>
       </c>
@@ -19065,6 +20307,10 @@
       <c r="C445" t="s">
         <v>1809</v>
       </c>
+      <c r="D445" t="str">
+        <f t="shared" si="12"/>
+        <v>RuleCondition</v>
+      </c>
       <c r="E445" t="s">
         <v>1810</v>
       </c>
@@ -19074,8 +20320,12 @@
       <c r="G445" t="s">
         <v>1813</v>
       </c>
-    </row>
-    <row r="446" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H445" t="str">
+        <f t="shared" si="13"/>
+        <v>RuleCondition = 0x6679,</v>
+      </c>
+    </row>
+    <row r="446" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A446" t="s">
         <v>1816</v>
       </c>
@@ -19085,6 +20335,10 @@
       <c r="C446" t="s">
         <v>1814</v>
       </c>
+      <c r="D446" t="str">
+        <f t="shared" si="12"/>
+        <v>RuleError</v>
+      </c>
       <c r="E446" t="s">
         <v>1815</v>
       </c>
@@ -19094,8 +20348,12 @@
       <c r="G446" t="s">
         <v>1817</v>
       </c>
-    </row>
-    <row r="447" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H446" t="str">
+        <f t="shared" si="13"/>
+        <v>RuleError = 0x6648,</v>
+      </c>
+    </row>
+    <row r="447" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A447" t="s">
         <v>1820</v>
       </c>
@@ -19105,6 +20363,10 @@
       <c r="C447" t="s">
         <v>1818</v>
       </c>
+      <c r="D447" t="str">
+        <f t="shared" si="12"/>
+        <v>RuleFolderEntryId</v>
+      </c>
       <c r="E447" t="s">
         <v>1819</v>
       </c>
@@ -19114,8 +20376,12 @@
       <c r="G447" t="s">
         <v>1821</v>
       </c>
-    </row>
-    <row r="448" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H447" t="str">
+        <f t="shared" si="13"/>
+        <v>RuleFolderEntryId = 0x6651,</v>
+      </c>
+    </row>
+    <row r="448" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A448" t="s">
         <v>1824</v>
       </c>
@@ -19125,6 +20391,10 @@
       <c r="C448" t="s">
         <v>1822</v>
       </c>
+      <c r="D448" t="str">
+        <f t="shared" si="12"/>
+        <v>RuleId</v>
+      </c>
       <c r="E448" t="s">
         <v>1823</v>
       </c>
@@ -19134,8 +20404,12 @@
       <c r="G448" t="s">
         <v>1825</v>
       </c>
-    </row>
-    <row r="449" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H448" t="str">
+        <f t="shared" si="13"/>
+        <v>RuleId = 0x6674,</v>
+      </c>
+    </row>
+    <row r="449" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A449" t="s">
         <v>1828</v>
       </c>
@@ -19145,6 +20419,10 @@
       <c r="C449" t="s">
         <v>1826</v>
       </c>
+      <c r="D449" t="str">
+        <f t="shared" si="12"/>
+        <v>RuleIds</v>
+      </c>
       <c r="E449" t="s">
         <v>1827</v>
       </c>
@@ -19154,8 +20432,12 @@
       <c r="G449" t="s">
         <v>1829</v>
       </c>
-    </row>
-    <row r="450" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H449" t="str">
+        <f t="shared" si="13"/>
+        <v>RuleIds = 0x6675,</v>
+      </c>
+    </row>
+    <row r="450" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A450" t="s">
         <v>1832</v>
       </c>
@@ -19165,6 +20447,10 @@
       <c r="C450" t="s">
         <v>1830</v>
       </c>
+      <c r="D450" t="str">
+        <f t="shared" si="12"/>
+        <v>RuleLevel</v>
+      </c>
       <c r="E450" t="s">
         <v>1831</v>
       </c>
@@ -19174,8 +20460,12 @@
       <c r="G450" t="s">
         <v>1833</v>
       </c>
-    </row>
-    <row r="451" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H450" t="str">
+        <f t="shared" si="13"/>
+        <v>RuleLevel = 0x6683,</v>
+      </c>
+    </row>
+    <row r="451" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A451" t="s">
         <v>1836</v>
       </c>
@@ -19185,6 +20475,10 @@
       <c r="C451" t="s">
         <v>1834</v>
       </c>
+      <c r="D451" t="str">
+        <f t="shared" ref="D451:D514" si="14">RIGHT(C451,LEN(C451)-6)</f>
+        <v>RuleMessageLevel</v>
+      </c>
       <c r="E451" t="s">
         <v>1835</v>
       </c>
@@ -19194,8 +20488,12 @@
       <c r="G451" t="s">
         <v>1837</v>
       </c>
-    </row>
-    <row r="452" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H451" t="str">
+        <f t="shared" ref="H451:H514" si="15">D451 &amp; " = " &amp; A451 &amp; ","</f>
+        <v>RuleMessageLevel = 0x65ED,</v>
+      </c>
+    </row>
+    <row r="452" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A452" t="s">
         <v>1840</v>
       </c>
@@ -19205,6 +20503,10 @@
       <c r="C452" t="s">
         <v>1838</v>
       </c>
+      <c r="D452" t="str">
+        <f t="shared" si="14"/>
+        <v>RuleMessageName</v>
+      </c>
       <c r="E452" t="s">
         <v>1839</v>
       </c>
@@ -19214,8 +20516,12 @@
       <c r="G452" t="s">
         <v>1841</v>
       </c>
-    </row>
-    <row r="453" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H452" t="str">
+        <f t="shared" si="15"/>
+        <v>RuleMessageName = 0x65EC,</v>
+      </c>
+    </row>
+    <row r="453" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A453" t="s">
         <v>1844</v>
       </c>
@@ -19225,6 +20531,10 @@
       <c r="C453" t="s">
         <v>1842</v>
       </c>
+      <c r="D453" t="str">
+        <f t="shared" si="14"/>
+        <v>RuleMessageProvider</v>
+      </c>
       <c r="E453" t="s">
         <v>1843</v>
       </c>
@@ -19234,8 +20544,12 @@
       <c r="G453" t="s">
         <v>1845</v>
       </c>
-    </row>
-    <row r="454" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H453" t="str">
+        <f t="shared" si="15"/>
+        <v>RuleMessageProvider = 0x65EB,</v>
+      </c>
+    </row>
+    <row r="454" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A454" t="s">
         <v>1848</v>
       </c>
@@ -19245,6 +20559,10 @@
       <c r="C454" t="s">
         <v>1846</v>
       </c>
+      <c r="D454" t="str">
+        <f t="shared" si="14"/>
+        <v>RuleMessageProviderData</v>
+      </c>
       <c r="E454" t="s">
         <v>1847</v>
       </c>
@@ -19254,8 +20572,12 @@
       <c r="G454" t="s">
         <v>1849</v>
       </c>
-    </row>
-    <row r="455" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H454" t="str">
+        <f t="shared" si="15"/>
+        <v>RuleMessageProviderData = 0x65EE,</v>
+      </c>
+    </row>
+    <row r="455" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A455" t="s">
         <v>1852</v>
       </c>
@@ -19265,6 +20587,10 @@
       <c r="C455" t="s">
         <v>1850</v>
       </c>
+      <c r="D455" t="str">
+        <f t="shared" si="14"/>
+        <v>RuleMessageSequence</v>
+      </c>
       <c r="E455" t="s">
         <v>1851</v>
       </c>
@@ -19274,8 +20600,12 @@
       <c r="G455" t="s">
         <v>1853</v>
       </c>
-    </row>
-    <row r="456" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H455" t="str">
+        <f t="shared" si="15"/>
+        <v>RuleMessageSequence = 0x65F3,</v>
+      </c>
+    </row>
+    <row r="456" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A456" t="s">
         <v>1856</v>
       </c>
@@ -19285,6 +20615,10 @@
       <c r="C456" t="s">
         <v>1854</v>
       </c>
+      <c r="D456" t="str">
+        <f t="shared" si="14"/>
+        <v>RuleMessageState</v>
+      </c>
       <c r="E456" t="s">
         <v>1855</v>
       </c>
@@ -19294,8 +20628,12 @@
       <c r="G456" t="s">
         <v>1857</v>
       </c>
-    </row>
-    <row r="457" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H456" t="str">
+        <f t="shared" si="15"/>
+        <v>RuleMessageState = 0x65E9,</v>
+      </c>
+    </row>
+    <row r="457" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A457" t="s">
         <v>1860</v>
       </c>
@@ -19305,6 +20643,10 @@
       <c r="C457" t="s">
         <v>1858</v>
       </c>
+      <c r="D457" t="str">
+        <f t="shared" si="14"/>
+        <v>RuleMessageUserFlags</v>
+      </c>
       <c r="E457" t="s">
         <v>1859</v>
       </c>
@@ -19314,8 +20656,12 @@
       <c r="G457" t="s">
         <v>1861</v>
       </c>
-    </row>
-    <row r="458" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H457" t="str">
+        <f t="shared" si="15"/>
+        <v>RuleMessageUserFlags = 0x65EA,</v>
+      </c>
+    </row>
+    <row r="458" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A458" t="s">
         <v>1864</v>
       </c>
@@ -19325,6 +20671,10 @@
       <c r="C458" t="s">
         <v>1862</v>
       </c>
+      <c r="D458" t="str">
+        <f t="shared" si="14"/>
+        <v>RuleName</v>
+      </c>
       <c r="E458" t="s">
         <v>1863</v>
       </c>
@@ -19334,8 +20684,12 @@
       <c r="G458" t="s">
         <v>1865</v>
       </c>
-    </row>
-    <row r="459" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H458" t="str">
+        <f t="shared" si="15"/>
+        <v>RuleName = 0x6682,</v>
+      </c>
+    </row>
+    <row r="459" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A459" t="s">
         <v>1868</v>
       </c>
@@ -19345,6 +20699,10 @@
       <c r="C459" t="s">
         <v>1866</v>
       </c>
+      <c r="D459" t="str">
+        <f t="shared" si="14"/>
+        <v>RuleProvider</v>
+      </c>
       <c r="E459" t="s">
         <v>1867</v>
       </c>
@@ -19354,8 +20712,12 @@
       <c r="G459" t="s">
         <v>1869</v>
       </c>
-    </row>
-    <row r="460" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H459" t="str">
+        <f t="shared" si="15"/>
+        <v>RuleProvider = 0x6681,</v>
+      </c>
+    </row>
+    <row r="460" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A460" t="s">
         <v>1872</v>
       </c>
@@ -19365,6 +20727,10 @@
       <c r="C460" t="s">
         <v>1870</v>
       </c>
+      <c r="D460" t="str">
+        <f t="shared" si="14"/>
+        <v>RuleProviderData</v>
+      </c>
       <c r="E460" t="s">
         <v>1871</v>
       </c>
@@ -19374,8 +20740,12 @@
       <c r="G460" t="s">
         <v>1873</v>
       </c>
-    </row>
-    <row r="461" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H460" t="str">
+        <f t="shared" si="15"/>
+        <v>RuleProviderData = 0x6684,</v>
+      </c>
+    </row>
+    <row r="461" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A461" t="s">
         <v>1876</v>
       </c>
@@ -19385,6 +20755,10 @@
       <c r="C461" t="s">
         <v>1874</v>
       </c>
+      <c r="D461" t="str">
+        <f t="shared" si="14"/>
+        <v>RuleSequence</v>
+      </c>
       <c r="E461" t="s">
         <v>1875</v>
       </c>
@@ -19394,8 +20768,12 @@
       <c r="G461" t="s">
         <v>1877</v>
       </c>
-    </row>
-    <row r="462" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H461" t="str">
+        <f t="shared" si="15"/>
+        <v>RuleSequence = 0x6676,</v>
+      </c>
+    </row>
+    <row r="462" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A462" t="s">
         <v>1880</v>
       </c>
@@ -19405,6 +20783,10 @@
       <c r="C462" t="s">
         <v>1878</v>
       </c>
+      <c r="D462" t="str">
+        <f t="shared" si="14"/>
+        <v>RuleState</v>
+      </c>
       <c r="E462" t="s">
         <v>1879</v>
       </c>
@@ -19414,8 +20796,12 @@
       <c r="G462" t="s">
         <v>1881</v>
       </c>
-    </row>
-    <row r="463" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H462" t="str">
+        <f t="shared" si="15"/>
+        <v>RuleState = 0x6677,</v>
+      </c>
+    </row>
+    <row r="463" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A463" t="s">
         <v>1884</v>
       </c>
@@ -19425,6 +20811,10 @@
       <c r="C463" t="s">
         <v>1882</v>
       </c>
+      <c r="D463" t="str">
+        <f t="shared" si="14"/>
+        <v>RuleUserFlags</v>
+      </c>
       <c r="E463" t="s">
         <v>1883</v>
       </c>
@@ -19434,8 +20824,12 @@
       <c r="G463" t="s">
         <v>1885</v>
       </c>
-    </row>
-    <row r="464" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H463" t="str">
+        <f t="shared" si="15"/>
+        <v>RuleUserFlags = 0x6678,</v>
+      </c>
+    </row>
+    <row r="464" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A464" t="s">
         <v>1285</v>
       </c>
@@ -19445,6 +20839,10 @@
       <c r="C464" t="s">
         <v>1886</v>
       </c>
+      <c r="D464" t="str">
+        <f t="shared" si="14"/>
+        <v>RwRulesStream</v>
+      </c>
       <c r="E464" t="s">
         <v>1887</v>
       </c>
@@ -19454,8 +20852,12 @@
       <c r="G464" t="s">
         <v>1889</v>
       </c>
-    </row>
-    <row r="465" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H464" t="str">
+        <f t="shared" si="15"/>
+        <v>RwRulesStream = 0x6802,</v>
+      </c>
+    </row>
+    <row r="465" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A465" t="s">
         <v>1892</v>
       </c>
@@ -19465,6 +20867,10 @@
       <c r="C465" t="s">
         <v>1890</v>
       </c>
+      <c r="D465" t="str">
+        <f t="shared" si="14"/>
+        <v>ScheduleInfoAppointmentTombstone</v>
+      </c>
       <c r="E465" t="s">
         <v>1891</v>
       </c>
@@ -19474,8 +20880,12 @@
       <c r="G465" t="s">
         <v>1893</v>
       </c>
-    </row>
-    <row r="466" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H465" t="str">
+        <f t="shared" si="15"/>
+        <v>ScheduleInfoAppointmentTombstone = 0x686A,</v>
+      </c>
+    </row>
+    <row r="466" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A466" t="s">
         <v>1896</v>
       </c>
@@ -19485,6 +20895,10 @@
       <c r="C466" t="s">
         <v>1894</v>
       </c>
+      <c r="D466" t="str">
+        <f t="shared" si="14"/>
+        <v>ScheduleInfoAutoAcceptAppointments</v>
+      </c>
       <c r="E466" t="s">
         <v>1895</v>
       </c>
@@ -19494,8 +20908,12 @@
       <c r="G466" t="s">
         <v>1897</v>
       </c>
-    </row>
-    <row r="467" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H466" t="str">
+        <f t="shared" si="15"/>
+        <v>ScheduleInfoAutoAcceptAppointments = 0x686D,</v>
+      </c>
+    </row>
+    <row r="467" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A467" t="s">
         <v>1900</v>
       </c>
@@ -19505,6 +20923,10 @@
       <c r="C467" t="s">
         <v>1898</v>
       </c>
+      <c r="D467" t="str">
+        <f t="shared" si="14"/>
+        <v>ScheduleInfoDelegateEntryIds</v>
+      </c>
       <c r="E467" t="s">
         <v>1899</v>
       </c>
@@ -19514,8 +20936,12 @@
       <c r="G467" t="s">
         <v>1901</v>
       </c>
-    </row>
-    <row r="468" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H467" t="str">
+        <f t="shared" si="15"/>
+        <v>ScheduleInfoDelegateEntryIds = 0x6845,</v>
+      </c>
+    </row>
+    <row r="468" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A468" t="s">
         <v>1904</v>
       </c>
@@ -19525,6 +20951,10 @@
       <c r="C468" t="s">
         <v>1902</v>
       </c>
+      <c r="D468" t="str">
+        <f t="shared" si="14"/>
+        <v>ScheduleInfoDelegateNames</v>
+      </c>
       <c r="E468" t="s">
         <v>1903</v>
       </c>
@@ -19534,8 +20964,12 @@
       <c r="G468" t="s">
         <v>1905</v>
       </c>
-    </row>
-    <row r="469" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H468" t="str">
+        <f t="shared" si="15"/>
+        <v>ScheduleInfoDelegateNames = 0x6844,</v>
+      </c>
+    </row>
+    <row r="469" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A469" t="s">
         <v>1908</v>
       </c>
@@ -19545,6 +20979,10 @@
       <c r="C469" t="s">
         <v>1906</v>
       </c>
+      <c r="D469" t="str">
+        <f t="shared" si="14"/>
+        <v>ScheduleInfoDelegateNamesW</v>
+      </c>
       <c r="E469" t="s">
         <v>1907</v>
       </c>
@@ -19554,8 +20992,12 @@
       <c r="G469" t="s">
         <v>1909</v>
       </c>
-    </row>
-    <row r="470" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H469" t="str">
+        <f t="shared" si="15"/>
+        <v>ScheduleInfoDelegateNamesW = 0x684A,</v>
+      </c>
+    </row>
+    <row r="470" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A470" t="s">
         <v>1912</v>
       </c>
@@ -19565,6 +21007,10 @@
       <c r="C470" t="s">
         <v>1910</v>
       </c>
+      <c r="D470" t="str">
+        <f t="shared" si="14"/>
+        <v>ScheduleInfoDelegatorWantsCopy</v>
+      </c>
       <c r="E470" t="s">
         <v>1911</v>
       </c>
@@ -19574,8 +21020,12 @@
       <c r="G470" t="s">
         <v>1913</v>
       </c>
-    </row>
-    <row r="471" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H470" t="str">
+        <f t="shared" si="15"/>
+        <v>ScheduleInfoDelegatorWantsCopy = 0x6842,</v>
+      </c>
+    </row>
+    <row r="471" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A471" t="s">
         <v>1916</v>
       </c>
@@ -19585,6 +21035,10 @@
       <c r="C471" t="s">
         <v>1914</v>
       </c>
+      <c r="D471" t="str">
+        <f t="shared" si="14"/>
+        <v>ScheduleInfoDelegatorWantsInfo</v>
+      </c>
       <c r="E471" t="s">
         <v>1915</v>
       </c>
@@ -19594,8 +21048,12 @@
       <c r="G471" t="s">
         <v>1917</v>
       </c>
-    </row>
-    <row r="472" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H471" t="str">
+        <f t="shared" si="15"/>
+        <v>ScheduleInfoDelegatorWantsInfo = 0x684B,</v>
+      </c>
+    </row>
+    <row r="472" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A472" t="s">
         <v>1920</v>
       </c>
@@ -19605,6 +21063,10 @@
       <c r="C472" t="s">
         <v>1918</v>
       </c>
+      <c r="D472" t="str">
+        <f t="shared" si="14"/>
+        <v>ScheduleInfoDisallowOverlappingAppts</v>
+      </c>
       <c r="E472" t="s">
         <v>1919</v>
       </c>
@@ -19614,8 +21076,12 @@
       <c r="G472" t="s">
         <v>1921</v>
       </c>
-    </row>
-    <row r="473" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H472" t="str">
+        <f t="shared" si="15"/>
+        <v>ScheduleInfoDisallowOverlappingAppts = 0x686F,</v>
+      </c>
+    </row>
+    <row r="473" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A473" t="s">
         <v>1924</v>
       </c>
@@ -19625,6 +21091,10 @@
       <c r="C473" t="s">
         <v>1922</v>
       </c>
+      <c r="D473" t="str">
+        <f t="shared" si="14"/>
+        <v>ScheduleInfoDisallowRecurringAppts</v>
+      </c>
       <c r="E473" t="s">
         <v>1923</v>
       </c>
@@ -19634,8 +21104,12 @@
       <c r="G473" t="s">
         <v>1925</v>
       </c>
-    </row>
-    <row r="474" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H473" t="str">
+        <f t="shared" si="15"/>
+        <v>ScheduleInfoDisallowRecurringAppts = 0x686E,</v>
+      </c>
+    </row>
+    <row r="474" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A474" t="s">
         <v>1928</v>
       </c>
@@ -19645,6 +21119,10 @@
       <c r="C474" t="s">
         <v>1926</v>
       </c>
+      <c r="D474" t="str">
+        <f t="shared" si="14"/>
+        <v>ScheduleInfoDontMailDelegates</v>
+      </c>
       <c r="E474" t="s">
         <v>1927</v>
       </c>
@@ -19654,8 +21132,12 @@
       <c r="G474" t="s">
         <v>1929</v>
       </c>
-    </row>
-    <row r="475" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H474" t="str">
+        <f t="shared" si="15"/>
+        <v>ScheduleInfoDontMailDelegates = 0x6843,</v>
+      </c>
+    </row>
+    <row r="475" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A475" t="s">
         <v>1932</v>
       </c>
@@ -19665,6 +21147,10 @@
       <c r="C475" t="s">
         <v>1930</v>
       </c>
+      <c r="D475" t="str">
+        <f t="shared" si="14"/>
+        <v>ScheduleInfoFreeBusy</v>
+      </c>
       <c r="E475" t="s">
         <v>1931</v>
       </c>
@@ -19674,8 +21160,12 @@
       <c r="G475" t="s">
         <v>1933</v>
       </c>
-    </row>
-    <row r="476" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H475" t="str">
+        <f t="shared" si="15"/>
+        <v>ScheduleInfoFreeBusy = 0x686C,</v>
+      </c>
+    </row>
+    <row r="476" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A476" t="s">
         <v>1936</v>
       </c>
@@ -19685,6 +21175,10 @@
       <c r="C476" t="s">
         <v>1934</v>
       </c>
+      <c r="D476" t="str">
+        <f t="shared" si="14"/>
+        <v>ScheduleInfoFreeBusyAway</v>
+      </c>
       <c r="E476" t="s">
         <v>1935</v>
       </c>
@@ -19694,8 +21188,12 @@
       <c r="G476" t="s">
         <v>1937</v>
       </c>
-    </row>
-    <row r="477" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H476" t="str">
+        <f t="shared" si="15"/>
+        <v>ScheduleInfoFreeBusyAway = 0x6856,</v>
+      </c>
+    </row>
+    <row r="477" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A477" t="s">
         <v>1940</v>
       </c>
@@ -19705,6 +21203,10 @@
       <c r="C477" t="s">
         <v>1938</v>
       </c>
+      <c r="D477" t="str">
+        <f t="shared" si="14"/>
+        <v>ScheduleInfoFreeBusyBusy</v>
+      </c>
       <c r="E477" t="s">
         <v>1939</v>
       </c>
@@ -19714,8 +21216,12 @@
       <c r="G477" t="s">
         <v>1941</v>
       </c>
-    </row>
-    <row r="478" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H477" t="str">
+        <f t="shared" si="15"/>
+        <v>ScheduleInfoFreeBusyBusy = 0x6854,</v>
+      </c>
+    </row>
+    <row r="478" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A478" t="s">
         <v>1944</v>
       </c>
@@ -19725,6 +21231,10 @@
       <c r="C478" t="s">
         <v>1942</v>
       </c>
+      <c r="D478" t="str">
+        <f t="shared" si="14"/>
+        <v>ScheduleInfoFreeBusyMerged</v>
+      </c>
       <c r="E478" t="s">
         <v>1943</v>
       </c>
@@ -19734,8 +21244,12 @@
       <c r="G478" t="s">
         <v>1945</v>
       </c>
-    </row>
-    <row r="479" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H478" t="str">
+        <f t="shared" si="15"/>
+        <v>ScheduleInfoFreeBusyMerged = 0x6850,</v>
+      </c>
+    </row>
+    <row r="479" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A479" t="s">
         <v>1948</v>
       </c>
@@ -19745,6 +21259,10 @@
       <c r="C479" t="s">
         <v>1946</v>
       </c>
+      <c r="D479" t="str">
+        <f t="shared" si="14"/>
+        <v>ScheduleInfoFreeBusyTentative</v>
+      </c>
       <c r="E479" t="s">
         <v>1947</v>
       </c>
@@ -19754,8 +21272,12 @@
       <c r="G479" t="s">
         <v>1949</v>
       </c>
-    </row>
-    <row r="480" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H479" t="str">
+        <f t="shared" si="15"/>
+        <v>ScheduleInfoFreeBusyTentative = 0x6852,</v>
+      </c>
+    </row>
+    <row r="480" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A480" t="s">
         <v>1952</v>
       </c>
@@ -19765,6 +21287,10 @@
       <c r="C480" t="s">
         <v>1950</v>
       </c>
+      <c r="D480" t="str">
+        <f t="shared" si="14"/>
+        <v>ScheduleInfoMonthsAway</v>
+      </c>
       <c r="E480" t="s">
         <v>1951</v>
       </c>
@@ -19774,8 +21300,12 @@
       <c r="G480" t="s">
         <v>1953</v>
       </c>
-    </row>
-    <row r="481" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H480" t="str">
+        <f t="shared" si="15"/>
+        <v>ScheduleInfoMonthsAway = 0x6855,</v>
+      </c>
+    </row>
+    <row r="481" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A481" t="s">
         <v>1956</v>
       </c>
@@ -19785,6 +21315,10 @@
       <c r="C481" t="s">
         <v>1954</v>
       </c>
+      <c r="D481" t="str">
+        <f t="shared" si="14"/>
+        <v>ScheduleInfoMonthsBusy</v>
+      </c>
       <c r="E481" t="s">
         <v>1955</v>
       </c>
@@ -19794,8 +21328,12 @@
       <c r="G481" t="s">
         <v>1957</v>
       </c>
-    </row>
-    <row r="482" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H481" t="str">
+        <f t="shared" si="15"/>
+        <v>ScheduleInfoMonthsBusy = 0x6853,</v>
+      </c>
+    </row>
+    <row r="482" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A482" t="s">
         <v>1960</v>
       </c>
@@ -19805,6 +21343,10 @@
       <c r="C482" t="s">
         <v>1958</v>
       </c>
+      <c r="D482" t="str">
+        <f t="shared" si="14"/>
+        <v>ScheduleInfoMonthsMerged</v>
+      </c>
       <c r="E482" t="s">
         <v>1959</v>
       </c>
@@ -19814,8 +21356,12 @@
       <c r="G482" t="s">
         <v>1961</v>
       </c>
-    </row>
-    <row r="483" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H482" t="str">
+        <f t="shared" si="15"/>
+        <v>ScheduleInfoMonthsMerged = 0x684F,</v>
+      </c>
+    </row>
+    <row r="483" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A483" t="s">
         <v>1964</v>
       </c>
@@ -19825,6 +21371,10 @@
       <c r="C483" t="s">
         <v>1962</v>
       </c>
+      <c r="D483" t="str">
+        <f t="shared" si="14"/>
+        <v>ScheduleInfoMonthsTentative</v>
+      </c>
       <c r="E483" t="s">
         <v>1963</v>
       </c>
@@ -19834,8 +21384,12 @@
       <c r="G483" t="s">
         <v>1965</v>
       </c>
-    </row>
-    <row r="484" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H483" t="str">
+        <f t="shared" si="15"/>
+        <v>ScheduleInfoMonthsTentative = 0x6851,</v>
+      </c>
+    </row>
+    <row r="484" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A484" t="s">
         <v>1968</v>
       </c>
@@ -19845,6 +21399,10 @@
       <c r="C484" t="s">
         <v>1966</v>
       </c>
+      <c r="D484" t="str">
+        <f t="shared" si="14"/>
+        <v>ScheduleInfoResourceType</v>
+      </c>
       <c r="E484" t="s">
         <v>1967</v>
       </c>
@@ -19854,8 +21412,12 @@
       <c r="G484" t="s">
         <v>1969</v>
       </c>
-    </row>
-    <row r="485" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H484" t="str">
+        <f t="shared" si="15"/>
+        <v>ScheduleInfoResourceType = 0x6841,</v>
+      </c>
+    </row>
+    <row r="485" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A485" t="s">
         <v>1972</v>
       </c>
@@ -19865,6 +21427,10 @@
       <c r="C485" t="s">
         <v>1970</v>
       </c>
+      <c r="D485" t="str">
+        <f t="shared" si="14"/>
+        <v>SchedulePlusFreeBusyEntryId</v>
+      </c>
       <c r="E485" t="s">
         <v>1971</v>
       </c>
@@ -19874,8 +21440,12 @@
       <c r="G485" t="s">
         <v>1974</v>
       </c>
-    </row>
-    <row r="486" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H485" t="str">
+        <f t="shared" si="15"/>
+        <v>SchedulePlusFreeBusyEntryId = 0x6622,</v>
+      </c>
+    </row>
+    <row r="486" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A486" t="s">
         <v>446</v>
       </c>
@@ -19885,6 +21455,10 @@
       <c r="C486" t="s">
         <v>1975</v>
       </c>
+      <c r="D486" t="str">
+        <f t="shared" si="14"/>
+        <v>ScriptData</v>
+      </c>
       <c r="E486" t="s">
         <v>1976</v>
       </c>
@@ -19894,8 +21468,12 @@
       <c r="G486" t="s">
         <v>1977</v>
       </c>
-    </row>
-    <row r="487" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H486" t="str">
+        <f t="shared" si="15"/>
+        <v>ScriptData = 0x0004,</v>
+      </c>
+    </row>
+    <row r="487" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A487" t="s">
         <v>1900</v>
       </c>
@@ -19905,6 +21483,10 @@
       <c r="C487" t="s">
         <v>1978</v>
       </c>
+      <c r="D487" t="str">
+        <f t="shared" si="14"/>
+        <v>SearchFolderDefinition</v>
+      </c>
       <c r="E487" t="s">
         <v>1979</v>
       </c>
@@ -19914,8 +21496,12 @@
       <c r="G487" t="s">
         <v>1981</v>
       </c>
-    </row>
-    <row r="488" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H487" t="str">
+        <f t="shared" si="15"/>
+        <v>SearchFolderDefinition = 0x6845,</v>
+      </c>
+    </row>
+    <row r="488" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A488" t="s">
         <v>855</v>
       </c>
@@ -19925,6 +21511,10 @@
       <c r="C488" t="s">
         <v>1982</v>
       </c>
+      <c r="D488" t="str">
+        <f t="shared" si="14"/>
+        <v>SearchFolderEfpFlags</v>
+      </c>
       <c r="E488" t="s">
         <v>1983</v>
       </c>
@@ -19934,8 +21524,12 @@
       <c r="G488" t="s">
         <v>1984</v>
       </c>
-    </row>
-    <row r="489" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H488" t="str">
+        <f t="shared" si="15"/>
+        <v>SearchFolderEfpFlags = 0x6848,</v>
+      </c>
+    </row>
+    <row r="489" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A489" t="s">
         <v>1987</v>
       </c>
@@ -19945,6 +21539,10 @@
       <c r="C489" t="s">
         <v>1985</v>
       </c>
+      <c r="D489" t="str">
+        <f t="shared" si="14"/>
+        <v>SearchFolderExpiration</v>
+      </c>
       <c r="E489" t="s">
         <v>1986</v>
       </c>
@@ -19954,8 +21552,12 @@
       <c r="G489" t="s">
         <v>1988</v>
       </c>
-    </row>
-    <row r="490" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H489" t="str">
+        <f t="shared" si="15"/>
+        <v>SearchFolderExpiration = 0x683A,</v>
+      </c>
+    </row>
+    <row r="490" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A490" t="s">
         <v>1912</v>
       </c>
@@ -19965,6 +21567,10 @@
       <c r="C490" t="s">
         <v>1989</v>
       </c>
+      <c r="D490" t="str">
+        <f t="shared" si="14"/>
+        <v>SearchFolderId</v>
+      </c>
       <c r="E490" t="s">
         <v>1990</v>
       </c>
@@ -19974,8 +21580,12 @@
       <c r="G490" t="s">
         <v>1991</v>
       </c>
-    </row>
-    <row r="491" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H490" t="str">
+        <f t="shared" si="15"/>
+        <v>SearchFolderId = 0x6842,</v>
+      </c>
+    </row>
+    <row r="491" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A491" t="s">
         <v>1994</v>
       </c>
@@ -19985,6 +21595,10 @@
       <c r="C491" t="s">
         <v>1992</v>
       </c>
+      <c r="D491" t="str">
+        <f t="shared" si="14"/>
+        <v>SearchFolderLastUsed</v>
+      </c>
       <c r="E491" t="s">
         <v>1993</v>
       </c>
@@ -19994,8 +21608,12 @@
       <c r="G491" t="s">
         <v>1995</v>
       </c>
-    </row>
-    <row r="492" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H491" t="str">
+        <f t="shared" si="15"/>
+        <v>SearchFolderLastUsed = 0x6834,</v>
+      </c>
+    </row>
+    <row r="492" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A492" t="s">
         <v>1904</v>
       </c>
@@ -20005,6 +21623,10 @@
       <c r="C492" t="s">
         <v>1996</v>
       </c>
+      <c r="D492" t="str">
+        <f t="shared" si="14"/>
+        <v>SearchFolderRecreateInfo</v>
+      </c>
       <c r="E492" t="s">
         <v>1997</v>
       </c>
@@ -20014,8 +21636,12 @@
       <c r="G492" t="s">
         <v>1998</v>
       </c>
-    </row>
-    <row r="493" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H492" t="str">
+        <f t="shared" si="15"/>
+        <v>SearchFolderRecreateInfo = 0x6844,</v>
+      </c>
+    </row>
+    <row r="493" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A493" t="s">
         <v>872</v>
       </c>
@@ -20025,6 +21651,10 @@
       <c r="C493" t="s">
         <v>1999</v>
       </c>
+      <c r="D493" t="str">
+        <f t="shared" si="14"/>
+        <v>SearchFolderStorageType</v>
+      </c>
       <c r="E493" t="s">
         <v>2000</v>
       </c>
@@ -20034,8 +21664,12 @@
       <c r="G493" t="s">
         <v>2001</v>
       </c>
-    </row>
-    <row r="494" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H493" t="str">
+        <f t="shared" si="15"/>
+        <v>SearchFolderStorageType = 0x6846,</v>
+      </c>
+    </row>
+    <row r="494" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A494" t="s">
         <v>860</v>
       </c>
@@ -20045,6 +21679,10 @@
       <c r="C494" t="s">
         <v>2002</v>
       </c>
+      <c r="D494" t="str">
+        <f t="shared" si="14"/>
+        <v>SearchFolderTag</v>
+      </c>
       <c r="E494" t="s">
         <v>2003</v>
       </c>
@@ -20054,8 +21692,12 @@
       <c r="G494" t="s">
         <v>2004</v>
       </c>
-    </row>
-    <row r="495" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H494" t="str">
+        <f t="shared" si="15"/>
+        <v>SearchFolderTag = 0x6847,</v>
+      </c>
+    </row>
+    <row r="495" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A495" t="s">
         <v>1968</v>
       </c>
@@ -20065,6 +21707,10 @@
       <c r="C495" t="s">
         <v>2005</v>
       </c>
+      <c r="D495" t="str">
+        <f t="shared" si="14"/>
+        <v>SearchFolderTemplateId</v>
+      </c>
       <c r="E495" t="s">
         <v>2006</v>
       </c>
@@ -20074,8 +21720,12 @@
       <c r="G495" t="s">
         <v>2007</v>
       </c>
-    </row>
-    <row r="496" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H495" t="str">
+        <f t="shared" si="15"/>
+        <v>SearchFolderTemplateId = 0x6841,</v>
+      </c>
+    </row>
+    <row r="496" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A496" t="s">
         <v>2010</v>
       </c>
@@ -20085,6 +21735,10 @@
       <c r="C496" t="s">
         <v>2008</v>
       </c>
+      <c r="D496" t="str">
+        <f t="shared" si="14"/>
+        <v>SearchKey</v>
+      </c>
       <c r="E496" t="s">
         <v>2009</v>
       </c>
@@ -20094,8 +21748,12 @@
       <c r="G496" t="s">
         <v>2011</v>
       </c>
-    </row>
-    <row r="497" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H496" t="str">
+        <f t="shared" si="15"/>
+        <v>SearchKey = 0x300B,</v>
+      </c>
+    </row>
+    <row r="497" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A497" t="s">
         <v>2014</v>
       </c>
@@ -20105,6 +21763,10 @@
       <c r="C497" t="s">
         <v>2012</v>
       </c>
+      <c r="D497" t="str">
+        <f t="shared" si="14"/>
+        <v>SecurityDescriptorAsXml</v>
+      </c>
       <c r="E497" t="s">
         <v>2013</v>
       </c>
@@ -20114,8 +21776,12 @@
       <c r="G497" t="s">
         <v>2015</v>
       </c>
-    </row>
-    <row r="498" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H497" t="str">
+        <f t="shared" si="15"/>
+        <v>SecurityDescriptorAsXml = 0x0E6A,</v>
+      </c>
+    </row>
+    <row r="498" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A498" t="s">
         <v>2017</v>
       </c>
@@ -20125,6 +21791,10 @@
       <c r="C498" t="s">
         <v>2016</v>
       </c>
+      <c r="D498" t="str">
+        <f t="shared" si="14"/>
+        <v>Selectable</v>
+      </c>
       <c r="E498" t="s">
         <v>21</v>
       </c>
@@ -20134,8 +21804,12 @@
       <c r="G498" t="s">
         <v>2019</v>
       </c>
-    </row>
-    <row r="499" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H498" t="str">
+        <f t="shared" si="15"/>
+        <v>Selectable = 0x3609,</v>
+      </c>
+    </row>
+    <row r="499" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A499" t="s">
         <v>2022</v>
       </c>
@@ -20145,6 +21819,10 @@
       <c r="C499" t="s">
         <v>2020</v>
       </c>
+      <c r="D499" t="str">
+        <f t="shared" si="14"/>
+        <v>SenderAddressType</v>
+      </c>
       <c r="E499" t="s">
         <v>2021</v>
       </c>
@@ -20154,8 +21832,12 @@
       <c r="G499" t="s">
         <v>2023</v>
       </c>
-    </row>
-    <row r="500" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H499" t="str">
+        <f t="shared" si="15"/>
+        <v>SenderAddressType = 0x0C1E,</v>
+      </c>
+    </row>
+    <row r="500" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A500" t="s">
         <v>2026</v>
       </c>
@@ -20165,6 +21847,10 @@
       <c r="C500" t="s">
         <v>2024</v>
       </c>
+      <c r="D500" t="str">
+        <f t="shared" si="14"/>
+        <v>SenderEmailAddress</v>
+      </c>
       <c r="E500" t="s">
         <v>2025</v>
       </c>
@@ -20174,8 +21860,12 @@
       <c r="G500" t="s">
         <v>2027</v>
       </c>
-    </row>
-    <row r="501" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H500" t="str">
+        <f t="shared" si="15"/>
+        <v>SenderEmailAddress = 0x0C1F,</v>
+      </c>
+    </row>
+    <row r="501" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A501" t="s">
         <v>2030</v>
       </c>
@@ -20185,6 +21875,10 @@
       <c r="C501" t="s">
         <v>2028</v>
       </c>
+      <c r="D501" t="str">
+        <f t="shared" si="14"/>
+        <v>SenderEntryId</v>
+      </c>
       <c r="E501" t="s">
         <v>2029</v>
       </c>
@@ -20194,8 +21888,12 @@
       <c r="G501" t="s">
         <v>2031</v>
       </c>
-    </row>
-    <row r="502" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H501" t="str">
+        <f t="shared" si="15"/>
+        <v>SenderEntryId = 0x0C19,</v>
+      </c>
+    </row>
+    <row r="502" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A502" t="s">
         <v>2034</v>
       </c>
@@ -20205,6 +21903,10 @@
       <c r="C502" t="s">
         <v>2032</v>
       </c>
+      <c r="D502" t="str">
+        <f t="shared" si="14"/>
+        <v>SenderIdStatus</v>
+      </c>
       <c r="E502" t="s">
         <v>2033</v>
       </c>
@@ -20214,8 +21916,12 @@
       <c r="G502" t="s">
         <v>2035</v>
       </c>
-    </row>
-    <row r="503" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H502" t="str">
+        <f t="shared" si="15"/>
+        <v>SenderIdStatus = 0x4079,</v>
+      </c>
+    </row>
+    <row r="503" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A503" t="s">
         <v>2038</v>
       </c>
@@ -20225,6 +21931,10 @@
       <c r="C503" t="s">
         <v>2036</v>
       </c>
+      <c r="D503" t="str">
+        <f t="shared" si="14"/>
+        <v>SenderName</v>
+      </c>
       <c r="E503" t="s">
         <v>2037</v>
       </c>
@@ -20234,8 +21944,12 @@
       <c r="G503" t="s">
         <v>2039</v>
       </c>
-    </row>
-    <row r="504" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H503" t="str">
+        <f t="shared" si="15"/>
+        <v>SenderName = 0x0C1A,</v>
+      </c>
+    </row>
+    <row r="504" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A504" t="s">
         <v>2042</v>
       </c>
@@ -20245,6 +21959,10 @@
       <c r="C504" t="s">
         <v>2040</v>
       </c>
+      <c r="D504" t="str">
+        <f t="shared" si="14"/>
+        <v>SenderSearchKey</v>
+      </c>
       <c r="E504" t="s">
         <v>2041</v>
       </c>
@@ -20254,8 +21972,12 @@
       <c r="G504" t="s">
         <v>2043</v>
       </c>
-    </row>
-    <row r="505" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H504" t="str">
+        <f t="shared" si="15"/>
+        <v>SenderSearchKey = 0x0C1D,</v>
+      </c>
+    </row>
+    <row r="505" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A505" t="s">
         <v>2046</v>
       </c>
@@ -20265,6 +21987,10 @@
       <c r="C505" t="s">
         <v>2044</v>
       </c>
+      <c r="D505" t="str">
+        <f t="shared" si="14"/>
+        <v>SenderSmtpAddress</v>
+      </c>
       <c r="E505" t="s">
         <v>2045</v>
       </c>
@@ -20274,8 +22000,12 @@
       <c r="G505" t="s">
         <v>2047</v>
       </c>
-    </row>
-    <row r="506" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H505" t="str">
+        <f t="shared" si="15"/>
+        <v>SenderSmtpAddress = 0x5D01,</v>
+      </c>
+    </row>
+    <row r="506" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A506" t="s">
         <v>1285</v>
       </c>
@@ -20285,6 +22015,10 @@
       <c r="C506" t="s">
         <v>2048</v>
       </c>
+      <c r="D506" t="str">
+        <f t="shared" si="14"/>
+        <v>SenderTelephoneNumber</v>
+      </c>
       <c r="E506" t="s">
         <v>35</v>
       </c>
@@ -20294,8 +22028,12 @@
       <c r="G506" t="s">
         <v>2049</v>
       </c>
-    </row>
-    <row r="507" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H506" t="str">
+        <f t="shared" si="15"/>
+        <v>SenderTelephoneNumber = 0x6802,</v>
+      </c>
+    </row>
+    <row r="507" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A507" t="s">
         <v>2052</v>
       </c>
@@ -20305,6 +22043,10 @@
       <c r="C507" t="s">
         <v>2050</v>
       </c>
+      <c r="D507" t="str">
+        <f t="shared" si="14"/>
+        <v>SendInternetEncoding</v>
+      </c>
       <c r="E507" t="s">
         <v>2051</v>
       </c>
@@ -20314,8 +22056,12 @@
       <c r="G507" t="s">
         <v>2053</v>
       </c>
-    </row>
-    <row r="508" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H507" t="str">
+        <f t="shared" si="15"/>
+        <v>SendInternetEncoding = 0x3A71,</v>
+      </c>
+    </row>
+    <row r="508" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A508" t="s">
         <v>2056</v>
       </c>
@@ -20325,6 +22071,10 @@
       <c r="C508" t="s">
         <v>2054</v>
       </c>
+      <c r="D508" t="str">
+        <f t="shared" si="14"/>
+        <v>SendRichInfo</v>
+      </c>
       <c r="E508" t="s">
         <v>2055</v>
       </c>
@@ -20334,8 +22084,12 @@
       <c r="G508" t="s">
         <v>2057</v>
       </c>
-    </row>
-    <row r="509" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H508" t="str">
+        <f t="shared" si="15"/>
+        <v>SendRichInfo = 0x3A40,</v>
+      </c>
+    </row>
+    <row r="509" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A509" t="s">
         <v>2060</v>
       </c>
@@ -20345,6 +22099,10 @@
       <c r="C509" t="s">
         <v>2058</v>
       </c>
+      <c r="D509" t="str">
+        <f t="shared" si="14"/>
+        <v>Sensitivity</v>
+      </c>
       <c r="E509" t="s">
         <v>2059</v>
       </c>
@@ -20354,8 +22112,12 @@
       <c r="G509" t="s">
         <v>2061</v>
       </c>
-    </row>
-    <row r="510" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H509" t="str">
+        <f t="shared" si="15"/>
+        <v>Sensitivity = 0x0036,</v>
+      </c>
+    </row>
+    <row r="510" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A510" t="s">
         <v>2064</v>
       </c>
@@ -20365,6 +22127,10 @@
       <c r="C510" t="s">
         <v>2062</v>
       </c>
+      <c r="D510" t="str">
+        <f t="shared" si="14"/>
+        <v>SentMailSvrEID</v>
+      </c>
       <c r="E510" t="s">
         <v>2063</v>
       </c>
@@ -20374,8 +22140,12 @@
       <c r="G510" t="s">
         <v>2065</v>
       </c>
-    </row>
-    <row r="511" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H510" t="str">
+        <f t="shared" si="15"/>
+        <v>SentMailSvrEID = 0x6740,</v>
+      </c>
+    </row>
+    <row r="511" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A511" t="s">
         <v>2068</v>
       </c>
@@ -20385,6 +22155,10 @@
       <c r="C511" t="s">
         <v>2066</v>
       </c>
+      <c r="D511" t="str">
+        <f t="shared" si="14"/>
+        <v>SentRepresentingAddressType</v>
+      </c>
       <c r="E511" t="s">
         <v>2067</v>
       </c>
@@ -20394,8 +22168,12 @@
       <c r="G511" t="s">
         <v>2069</v>
       </c>
-    </row>
-    <row r="512" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H511" t="str">
+        <f t="shared" si="15"/>
+        <v>SentRepresentingAddressType = 0x0064,</v>
+      </c>
+    </row>
+    <row r="512" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A512" t="s">
         <v>2072</v>
       </c>
@@ -20405,6 +22183,10 @@
       <c r="C512" t="s">
         <v>2070</v>
       </c>
+      <c r="D512" t="str">
+        <f t="shared" si="14"/>
+        <v>SentRepresentingEmailAddress</v>
+      </c>
       <c r="E512" t="s">
         <v>2071</v>
       </c>
@@ -20414,8 +22196,12 @@
       <c r="G512" t="s">
         <v>2047</v>
       </c>
-    </row>
-    <row r="513" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H512" t="str">
+        <f t="shared" si="15"/>
+        <v>SentRepresentingEmailAddress = 0x0065,</v>
+      </c>
+    </row>
+    <row r="513" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A513" t="s">
         <v>2075</v>
       </c>
@@ -20425,6 +22211,10 @@
       <c r="C513" t="s">
         <v>2073</v>
       </c>
+      <c r="D513" t="str">
+        <f t="shared" si="14"/>
+        <v>SentRepresentingEntryId</v>
+      </c>
       <c r="E513" t="s">
         <v>2074</v>
       </c>
@@ -20434,8 +22224,12 @@
       <c r="G513" t="s">
         <v>2076</v>
       </c>
-    </row>
-    <row r="514" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H513" t="str">
+        <f t="shared" si="15"/>
+        <v>SentRepresentingEntryId = 0x0041,</v>
+      </c>
+    </row>
+    <row r="514" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A514" t="s">
         <v>2078</v>
       </c>
@@ -20445,11 +22239,19 @@
       <c r="C514" t="s">
         <v>2077</v>
       </c>
+      <c r="D514" t="str">
+        <f t="shared" si="14"/>
+        <v>SentRepresentingFlags</v>
+      </c>
       <c r="F514" t="s">
         <v>809</v>
       </c>
-    </row>
-    <row r="515" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H514" t="str">
+        <f t="shared" si="15"/>
+        <v>SentRepresentingFlags = 0x401A,</v>
+      </c>
+    </row>
+    <row r="515" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A515" t="s">
         <v>2081</v>
       </c>
@@ -20459,6 +22261,10 @@
       <c r="C515" t="s">
         <v>2079</v>
       </c>
+      <c r="D515" t="str">
+        <f t="shared" ref="D515:D578" si="16">RIGHT(C515,LEN(C515)-6)</f>
+        <v>SentRepresentingName</v>
+      </c>
       <c r="E515" t="s">
         <v>2080</v>
       </c>
@@ -20468,8 +22274,12 @@
       <c r="G515" t="s">
         <v>2082</v>
       </c>
-    </row>
-    <row r="516" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H515" t="str">
+        <f t="shared" ref="H515:H578" si="17">D515 &amp; " = " &amp; A515 &amp; ","</f>
+        <v>SentRepresentingName = 0x0042,</v>
+      </c>
+    </row>
+    <row r="516" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A516" t="s">
         <v>2085</v>
       </c>
@@ -20479,6 +22289,10 @@
       <c r="C516" t="s">
         <v>2083</v>
       </c>
+      <c r="D516" t="str">
+        <f t="shared" si="16"/>
+        <v>SentRepresentingSearchKey</v>
+      </c>
       <c r="E516" t="s">
         <v>2084</v>
       </c>
@@ -20488,8 +22302,12 @@
       <c r="G516" t="s">
         <v>2086</v>
       </c>
-    </row>
-    <row r="517" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H516" t="str">
+        <f t="shared" si="17"/>
+        <v>SentRepresentingSearchKey = 0x003B,</v>
+      </c>
+    </row>
+    <row r="517" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A517" t="s">
         <v>2089</v>
       </c>
@@ -20499,6 +22317,10 @@
       <c r="C517" t="s">
         <v>2087</v>
       </c>
+      <c r="D517" t="str">
+        <f t="shared" si="16"/>
+        <v>SentRepresentingSmtpAddress</v>
+      </c>
       <c r="E517" t="s">
         <v>2088</v>
       </c>
@@ -20508,8 +22330,12 @@
       <c r="G517" t="s">
         <v>2090</v>
       </c>
-    </row>
-    <row r="518" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H517" t="str">
+        <f t="shared" si="17"/>
+        <v>SentRepresentingSmtpAddress = 0x5D02,</v>
+      </c>
+    </row>
+    <row r="518" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A518" t="s">
         <v>2093</v>
       </c>
@@ -20519,6 +22345,10 @@
       <c r="C518" t="s">
         <v>2091</v>
       </c>
+      <c r="D518" t="str">
+        <f t="shared" si="16"/>
+        <v>SerializedReplidGuidMap</v>
+      </c>
       <c r="E518" t="s">
         <v>2092</v>
       </c>
@@ -20528,8 +22358,12 @@
       <c r="G518" t="s">
         <v>2095</v>
       </c>
-    </row>
-    <row r="519" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H518" t="str">
+        <f t="shared" si="17"/>
+        <v>SerializedReplidGuidMap = 0x6638,</v>
+      </c>
+    </row>
+    <row r="519" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A519" t="s">
         <v>2098</v>
       </c>
@@ -20539,6 +22373,10 @@
       <c r="C519" t="s">
         <v>2096</v>
       </c>
+      <c r="D519" t="str">
+        <f t="shared" si="16"/>
+        <v>SmtpAddress</v>
+      </c>
       <c r="E519" t="s">
         <v>2097</v>
       </c>
@@ -20548,8 +22386,12 @@
       <c r="G519" t="s">
         <v>2099</v>
       </c>
-    </row>
-    <row r="520" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H519" t="str">
+        <f t="shared" si="17"/>
+        <v>SmtpAddress = 0x39FE,</v>
+      </c>
+    </row>
+    <row r="520" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A520" t="s">
         <v>2102</v>
       </c>
@@ -20559,6 +22401,10 @@
       <c r="C520" t="s">
         <v>2100</v>
       </c>
+      <c r="D520" t="str">
+        <f t="shared" si="16"/>
+        <v>SortLocaleId</v>
+      </c>
       <c r="E520" t="s">
         <v>2101</v>
       </c>
@@ -20568,8 +22414,12 @@
       <c r="G520" t="s">
         <v>2103</v>
       </c>
-    </row>
-    <row r="521" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H520" t="str">
+        <f t="shared" si="17"/>
+        <v>SortLocaleId = 0x6705,</v>
+      </c>
+    </row>
+    <row r="521" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A521" t="s">
         <v>2106</v>
       </c>
@@ -20579,6 +22429,10 @@
       <c r="C521" t="s">
         <v>2104</v>
       </c>
+      <c r="D521" t="str">
+        <f t="shared" si="16"/>
+        <v>SourceKey</v>
+      </c>
       <c r="E521" t="s">
         <v>2105</v>
       </c>
@@ -20588,8 +22442,12 @@
       <c r="G521" t="s">
         <v>2107</v>
       </c>
-    </row>
-    <row r="522" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H521" t="str">
+        <f t="shared" si="17"/>
+        <v>SourceKey = 0x65E0,</v>
+      </c>
+    </row>
+    <row r="522" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A522" t="s">
         <v>2110</v>
       </c>
@@ -20599,6 +22457,10 @@
       <c r="C522" t="s">
         <v>2108</v>
       </c>
+      <c r="D522" t="str">
+        <f t="shared" si="16"/>
+        <v>SpokenName</v>
+      </c>
       <c r="E522" t="s">
         <v>2109</v>
       </c>
@@ -20608,8 +22470,12 @@
       <c r="G522" t="s">
         <v>2111</v>
       </c>
-    </row>
-    <row r="523" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H522" t="str">
+        <f t="shared" si="17"/>
+        <v>SpokenName = 0x8CC2,</v>
+      </c>
+    </row>
+    <row r="523" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A523" t="s">
         <v>2114</v>
       </c>
@@ -20619,6 +22485,10 @@
       <c r="C523" t="s">
         <v>2112</v>
       </c>
+      <c r="D523" t="str">
+        <f t="shared" si="16"/>
+        <v>SpouseName</v>
+      </c>
       <c r="E523" t="s">
         <v>2113</v>
       </c>
@@ -20628,8 +22498,12 @@
       <c r="G523" t="s">
         <v>2115</v>
       </c>
-    </row>
-    <row r="524" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H523" t="str">
+        <f t="shared" si="17"/>
+        <v>SpouseName = 0x3A48,</v>
+      </c>
+    </row>
+    <row r="524" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A524" t="s">
         <v>2118</v>
       </c>
@@ -20639,6 +22513,10 @@
       <c r="C524" t="s">
         <v>2116</v>
       </c>
+      <c r="D524" t="str">
+        <f t="shared" si="16"/>
+        <v>StartDate</v>
+      </c>
       <c r="E524" t="s">
         <v>2117</v>
       </c>
@@ -20648,8 +22526,12 @@
       <c r="G524" t="s">
         <v>2119</v>
       </c>
-    </row>
-    <row r="525" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H524" t="str">
+        <f t="shared" si="17"/>
+        <v>StartDate = 0x0060,</v>
+      </c>
+    </row>
+    <row r="525" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A525" t="s">
         <v>2122</v>
       </c>
@@ -20659,6 +22541,10 @@
       <c r="C525" t="s">
         <v>2120</v>
       </c>
+      <c r="D525" t="str">
+        <f t="shared" si="16"/>
+        <v>StartDateEtc</v>
+      </c>
       <c r="E525" t="s">
         <v>2121</v>
       </c>
@@ -20668,8 +22554,12 @@
       <c r="G525" t="s">
         <v>2123</v>
       </c>
-    </row>
-    <row r="526" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H525" t="str">
+        <f t="shared" si="17"/>
+        <v>StartDateEtc = 0x301B,</v>
+      </c>
+    </row>
+    <row r="526" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A526" t="s">
         <v>2126</v>
       </c>
@@ -20679,6 +22569,10 @@
       <c r="C526" t="s">
         <v>2124</v>
       </c>
+      <c r="D526" t="str">
+        <f t="shared" si="16"/>
+        <v>StateOrProvince</v>
+      </c>
       <c r="E526" t="s">
         <v>2125</v>
       </c>
@@ -20688,8 +22582,12 @@
       <c r="G526" t="s">
         <v>2127</v>
       </c>
-    </row>
-    <row r="527" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H526" t="str">
+        <f t="shared" si="17"/>
+        <v>StateOrProvince = 0x3A28,</v>
+      </c>
+    </row>
+    <row r="527" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A527" t="s">
         <v>2130</v>
       </c>
@@ -20699,6 +22597,10 @@
       <c r="C527" t="s">
         <v>2128</v>
       </c>
+      <c r="D527" t="str">
+        <f t="shared" si="16"/>
+        <v>StoreEntryId</v>
+      </c>
       <c r="E527" t="s">
         <v>2129</v>
       </c>
@@ -20708,8 +22610,12 @@
       <c r="G527" t="s">
         <v>2131</v>
       </c>
-    </row>
-    <row r="528" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H527" t="str">
+        <f t="shared" si="17"/>
+        <v>StoreEntryId = 0x0FFB,</v>
+      </c>
+    </row>
+    <row r="528" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A528" t="s">
         <v>2134</v>
       </c>
@@ -20719,6 +22625,10 @@
       <c r="C528" t="s">
         <v>2132</v>
       </c>
+      <c r="D528" t="str">
+        <f t="shared" si="16"/>
+        <v>StoreState</v>
+      </c>
       <c r="E528" t="s">
         <v>2133</v>
       </c>
@@ -20728,8 +22638,12 @@
       <c r="G528" t="s">
         <v>2136</v>
       </c>
-    </row>
-    <row r="529" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H528" t="str">
+        <f t="shared" si="17"/>
+        <v>StoreState = 0x340E,</v>
+      </c>
+    </row>
+    <row r="529" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A529" t="s">
         <v>2139</v>
       </c>
@@ -20739,6 +22653,10 @@
       <c r="C529" t="s">
         <v>2137</v>
       </c>
+      <c r="D529" t="str">
+        <f t="shared" si="16"/>
+        <v>StoreSupportMask</v>
+      </c>
       <c r="E529" t="s">
         <v>2138</v>
       </c>
@@ -20748,8 +22666,12 @@
       <c r="G529" t="s">
         <v>2140</v>
       </c>
-    </row>
-    <row r="530" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H529" t="str">
+        <f t="shared" si="17"/>
+        <v>StoreSupportMask = 0x340D,</v>
+      </c>
+    </row>
+    <row r="530" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A530" t="s">
         <v>2143</v>
       </c>
@@ -20759,6 +22681,10 @@
       <c r="C530" t="s">
         <v>2141</v>
       </c>
+      <c r="D530" t="str">
+        <f t="shared" si="16"/>
+        <v>StreetAddress</v>
+      </c>
       <c r="E530" t="s">
         <v>2142</v>
       </c>
@@ -20768,8 +22694,12 @@
       <c r="G530" t="s">
         <v>2144</v>
       </c>
-    </row>
-    <row r="531" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H530" t="str">
+        <f t="shared" si="17"/>
+        <v>StreetAddress = 0x3A29,</v>
+      </c>
+    </row>
+    <row r="531" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A531" t="s">
         <v>2147</v>
       </c>
@@ -20779,6 +22709,10 @@
       <c r="C531" t="s">
         <v>2145</v>
       </c>
+      <c r="D531" t="str">
+        <f t="shared" si="16"/>
+        <v>Subfolders</v>
+      </c>
       <c r="E531" t="s">
         <v>2146</v>
       </c>
@@ -20788,8 +22722,12 @@
       <c r="G531" t="s">
         <v>2148</v>
       </c>
-    </row>
-    <row r="532" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H531" t="str">
+        <f t="shared" si="17"/>
+        <v>Subfolders = 0x360A,</v>
+      </c>
+    </row>
+    <row r="532" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A532" t="s">
         <v>2151</v>
       </c>
@@ -20799,6 +22737,10 @@
       <c r="C532" t="s">
         <v>2149</v>
       </c>
+      <c r="D532" t="str">
+        <f t="shared" si="16"/>
+        <v>Subject</v>
+      </c>
       <c r="E532" t="s">
         <v>2150</v>
       </c>
@@ -20808,8 +22750,12 @@
       <c r="G532" t="s">
         <v>2152</v>
       </c>
-    </row>
-    <row r="533" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H532" t="str">
+        <f t="shared" si="17"/>
+        <v>Subject = 0x0037,</v>
+      </c>
+    </row>
+    <row r="533" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A533" t="s">
         <v>2155</v>
       </c>
@@ -20819,6 +22765,10 @@
       <c r="C533" t="s">
         <v>2153</v>
       </c>
+      <c r="D533" t="str">
+        <f t="shared" si="16"/>
+        <v>SubjectPrefix</v>
+      </c>
       <c r="E533" t="s">
         <v>2154</v>
       </c>
@@ -20828,8 +22778,12 @@
       <c r="G533" t="s">
         <v>2156</v>
       </c>
-    </row>
-    <row r="534" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H533" t="str">
+        <f t="shared" si="17"/>
+        <v>SubjectPrefix = 0x003D,</v>
+      </c>
+    </row>
+    <row r="534" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A534" t="s">
         <v>2159</v>
       </c>
@@ -20839,6 +22793,10 @@
       <c r="C534" t="s">
         <v>2157</v>
       </c>
+      <c r="D534" t="str">
+        <f t="shared" si="16"/>
+        <v>SupplementaryInfo</v>
+      </c>
       <c r="E534" t="s">
         <v>2158</v>
       </c>
@@ -20848,8 +22806,12 @@
       <c r="G534" t="s">
         <v>2160</v>
       </c>
-    </row>
-    <row r="535" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H534" t="str">
+        <f t="shared" si="17"/>
+        <v>SupplementaryInfo = 0x0C1B,</v>
+      </c>
+    </row>
+    <row r="535" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A535" t="s">
         <v>2163</v>
       </c>
@@ -20859,6 +22821,10 @@
       <c r="C535" t="s">
         <v>2161</v>
       </c>
+      <c r="D535" t="str">
+        <f t="shared" si="16"/>
+        <v>Surname</v>
+      </c>
       <c r="E535" t="s">
         <v>2162</v>
       </c>
@@ -20868,8 +22834,12 @@
       <c r="G535" t="s">
         <v>2164</v>
       </c>
-    </row>
-    <row r="536" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H535" t="str">
+        <f t="shared" si="17"/>
+        <v>Surname = 0x3A11,</v>
+      </c>
+    </row>
+    <row r="536" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A536" t="s">
         <v>2167</v>
       </c>
@@ -20879,6 +22849,10 @@
       <c r="C536" t="s">
         <v>2165</v>
       </c>
+      <c r="D536" t="str">
+        <f t="shared" si="16"/>
+        <v>SwappedToDoData</v>
+      </c>
       <c r="E536" t="s">
         <v>2166</v>
       </c>
@@ -20888,8 +22862,12 @@
       <c r="G536" t="s">
         <v>2168</v>
       </c>
-    </row>
-    <row r="537" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H536" t="str">
+        <f t="shared" si="17"/>
+        <v>SwappedToDoData = 0x0E2D,</v>
+      </c>
+    </row>
+    <row r="537" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A537" t="s">
         <v>2171</v>
       </c>
@@ -20899,6 +22877,10 @@
       <c r="C537" t="s">
         <v>2169</v>
       </c>
+      <c r="D537" t="str">
+        <f t="shared" si="16"/>
+        <v>SwappedToDoStore</v>
+      </c>
       <c r="E537" t="s">
         <v>2170</v>
       </c>
@@ -20908,8 +22890,12 @@
       <c r="G537" t="s">
         <v>2172</v>
       </c>
-    </row>
-    <row r="538" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H537" t="str">
+        <f t="shared" si="17"/>
+        <v>SwappedToDoStore = 0x0E2C,</v>
+      </c>
+    </row>
+    <row r="538" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A538" t="s">
         <v>2175</v>
       </c>
@@ -20919,6 +22905,10 @@
       <c r="C538" t="s">
         <v>2173</v>
       </c>
+      <c r="D538" t="str">
+        <f t="shared" si="16"/>
+        <v>TargetEntryId</v>
+      </c>
       <c r="E538" t="s">
         <v>2174</v>
       </c>
@@ -20928,8 +22918,12 @@
       <c r="G538" t="s">
         <v>2176</v>
       </c>
-    </row>
-    <row r="539" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H538" t="str">
+        <f t="shared" si="17"/>
+        <v>TargetEntryId = 0x3010,</v>
+      </c>
+    </row>
+    <row r="539" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A539" t="s">
         <v>2179</v>
       </c>
@@ -20939,6 +22933,10 @@
       <c r="C539" t="s">
         <v>2177</v>
       </c>
+      <c r="D539" t="str">
+        <f t="shared" si="16"/>
+        <v>TelecommunicationsDeviceForDeafTelephoneNumber</v>
+      </c>
       <c r="E539" t="s">
         <v>2178</v>
       </c>
@@ -20948,8 +22946,12 @@
       <c r="G539" t="s">
         <v>2180</v>
       </c>
-    </row>
-    <row r="540" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H539" t="str">
+        <f t="shared" si="17"/>
+        <v>TelecommunicationsDeviceForDeafTelephoneNumber = 0x3A4B,</v>
+      </c>
+    </row>
+    <row r="540" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A540" t="s">
         <v>2183</v>
       </c>
@@ -20959,6 +22961,10 @@
       <c r="C540" t="s">
         <v>2181</v>
       </c>
+      <c r="D540" t="str">
+        <f t="shared" si="16"/>
+        <v>TelexNumber</v>
+      </c>
       <c r="E540" t="s">
         <v>2182</v>
       </c>
@@ -20968,8 +22974,12 @@
       <c r="G540" t="s">
         <v>2185</v>
       </c>
-    </row>
-    <row r="541" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H540" t="str">
+        <f t="shared" si="17"/>
+        <v>TelexNumber = 0x3A2C,</v>
+      </c>
+    </row>
+    <row r="541" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A541" t="s">
         <v>2188</v>
       </c>
@@ -20979,6 +22989,10 @@
       <c r="C541" t="s">
         <v>2186</v>
       </c>
+      <c r="D541" t="str">
+        <f t="shared" si="16"/>
+        <v>TemplateData</v>
+      </c>
       <c r="E541" t="s">
         <v>2187</v>
       </c>
@@ -20988,8 +23002,12 @@
       <c r="G541" t="s">
         <v>1977</v>
       </c>
-    </row>
-    <row r="542" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H541" t="str">
+        <f t="shared" si="17"/>
+        <v>TemplateData = 0x0001,</v>
+      </c>
+    </row>
+    <row r="542" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A542" t="s">
         <v>2191</v>
       </c>
@@ -20999,6 +23017,10 @@
       <c r="C542" t="s">
         <v>2189</v>
       </c>
+      <c r="D542" t="str">
+        <f t="shared" si="16"/>
+        <v>Templateid</v>
+      </c>
       <c r="E542" t="s">
         <v>2190</v>
       </c>
@@ -21008,8 +23030,12 @@
       <c r="G542" t="s">
         <v>2192</v>
       </c>
-    </row>
-    <row r="543" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H542" t="str">
+        <f t="shared" si="17"/>
+        <v>Templateid = 0x3902,</v>
+      </c>
+    </row>
+    <row r="543" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A543" t="s">
         <v>2195</v>
       </c>
@@ -21019,6 +23045,10 @@
       <c r="C543" t="s">
         <v>2193</v>
       </c>
+      <c r="D543" t="str">
+        <f t="shared" si="16"/>
+        <v>TextAttachmentCharset</v>
+      </c>
       <c r="E543" t="s">
         <v>2194</v>
       </c>
@@ -21028,8 +23058,12 @@
       <c r="G543" t="s">
         <v>2196</v>
       </c>
-    </row>
-    <row r="544" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H543" t="str">
+        <f t="shared" si="17"/>
+        <v>TextAttachmentCharset = 0x371B,</v>
+      </c>
+    </row>
+    <row r="544" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A544" t="s">
         <v>2199</v>
       </c>
@@ -21039,6 +23073,10 @@
       <c r="C544" t="s">
         <v>2197</v>
       </c>
+      <c r="D544" t="str">
+        <f t="shared" si="16"/>
+        <v>ThumbnailPhoto</v>
+      </c>
       <c r="E544" t="s">
         <v>2198</v>
       </c>
@@ -21048,8 +23086,12 @@
       <c r="G544" t="s">
         <v>2200</v>
       </c>
-    </row>
-    <row r="545" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H544" t="str">
+        <f t="shared" si="17"/>
+        <v>ThumbnailPhoto = 0x8C9E,</v>
+      </c>
+    </row>
+    <row r="545" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A545" t="s">
         <v>2203</v>
       </c>
@@ -21059,6 +23101,10 @@
       <c r="C545" t="s">
         <v>2201</v>
       </c>
+      <c r="D545" t="str">
+        <f t="shared" si="16"/>
+        <v>Title</v>
+      </c>
       <c r="E545" t="s">
         <v>2202</v>
       </c>
@@ -21068,8 +23114,12 @@
       <c r="G545" t="s">
         <v>2204</v>
       </c>
-    </row>
-    <row r="546" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H545" t="str">
+        <f t="shared" si="17"/>
+        <v>Title = 0x3A17,</v>
+      </c>
+    </row>
+    <row r="546" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A546" t="s">
         <v>2207</v>
       </c>
@@ -21079,6 +23129,10 @@
       <c r="C546" t="s">
         <v>2205</v>
       </c>
+      <c r="D546" t="str">
+        <f t="shared" si="16"/>
+        <v>TnefCorrelationKey</v>
+      </c>
       <c r="E546" t="s">
         <v>2206</v>
       </c>
@@ -21088,8 +23142,12 @@
       <c r="G546" t="s">
         <v>2208</v>
       </c>
-    </row>
-    <row r="547" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H546" t="str">
+        <f t="shared" si="17"/>
+        <v>TnefCorrelationKey = 0x007F,</v>
+      </c>
+    </row>
+    <row r="547" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A547" t="s">
         <v>2211</v>
       </c>
@@ -21099,6 +23157,10 @@
       <c r="C547" t="s">
         <v>2209</v>
       </c>
+      <c r="D547" t="str">
+        <f t="shared" si="16"/>
+        <v>ToDoItemFlags</v>
+      </c>
       <c r="E547" t="s">
         <v>2210</v>
       </c>
@@ -21108,8 +23170,12 @@
       <c r="G547" t="s">
         <v>2212</v>
       </c>
-    </row>
-    <row r="548" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H547" t="str">
+        <f t="shared" si="17"/>
+        <v>ToDoItemFlags = 0x0E2B,</v>
+      </c>
+    </row>
+    <row r="548" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A548" t="s">
         <v>2215</v>
       </c>
@@ -21119,6 +23185,10 @@
       <c r="C548" t="s">
         <v>2213</v>
       </c>
+      <c r="D548" t="str">
+        <f t="shared" si="16"/>
+        <v>TransmittableDisplayName</v>
+      </c>
       <c r="E548" t="s">
         <v>2214</v>
       </c>
@@ -21128,8 +23198,12 @@
       <c r="G548" t="s">
         <v>2216</v>
       </c>
-    </row>
-    <row r="549" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H548" t="str">
+        <f t="shared" si="17"/>
+        <v>TransmittableDisplayName = 0x3A20,</v>
+      </c>
+    </row>
+    <row r="549" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A549" t="s">
         <v>2219</v>
       </c>
@@ -21139,6 +23213,10 @@
       <c r="C549" t="s">
         <v>2217</v>
       </c>
+      <c r="D549" t="str">
+        <f t="shared" si="16"/>
+        <v>TransportMessageHeaders</v>
+      </c>
       <c r="E549" t="s">
         <v>2218</v>
       </c>
@@ -21148,8 +23226,12 @@
       <c r="G549" t="s">
         <v>2220</v>
       </c>
-    </row>
-    <row r="550" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H549" t="str">
+        <f t="shared" si="17"/>
+        <v>TransportMessageHeaders = 0x007D,</v>
+      </c>
+    </row>
+    <row r="550" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A550" t="s">
         <v>2223</v>
       </c>
@@ -21159,6 +23241,10 @@
       <c r="C550" t="s">
         <v>2221</v>
       </c>
+      <c r="D550" t="str">
+        <f t="shared" si="16"/>
+        <v>TrustSender</v>
+      </c>
       <c r="E550" t="s">
         <v>2222</v>
       </c>
@@ -21168,8 +23254,12 @@
       <c r="G550" t="s">
         <v>2224</v>
       </c>
-    </row>
-    <row r="551" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H550" t="str">
+        <f t="shared" si="17"/>
+        <v>TrustSender = 0x0E79,</v>
+      </c>
+    </row>
+    <row r="551" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A551" t="s">
         <v>2227</v>
       </c>
@@ -21179,6 +23269,10 @@
       <c r="C551" t="s">
         <v>2225</v>
       </c>
+      <c r="D551" t="str">
+        <f t="shared" si="16"/>
+        <v>UserCertificate</v>
+      </c>
       <c r="E551" t="s">
         <v>2226</v>
       </c>
@@ -21188,8 +23282,12 @@
       <c r="G551" t="s">
         <v>2228</v>
       </c>
-    </row>
-    <row r="552" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H551" t="str">
+        <f t="shared" si="17"/>
+        <v>UserCertificate = 0x3A22,</v>
+      </c>
+    </row>
+    <row r="552" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A552" t="s">
         <v>2231</v>
       </c>
@@ -21199,6 +23297,10 @@
       <c r="C552" t="s">
         <v>2229</v>
       </c>
+      <c r="D552" t="str">
+        <f t="shared" si="16"/>
+        <v>UserEntryId</v>
+      </c>
       <c r="E552" t="s">
         <v>2230</v>
       </c>
@@ -21208,8 +23310,12 @@
       <c r="G552" t="s">
         <v>2136</v>
       </c>
-    </row>
-    <row r="553" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H552" t="str">
+        <f t="shared" si="17"/>
+        <v>UserEntryId = 0x6619,</v>
+      </c>
+    </row>
+    <row r="553" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A553" t="s">
         <v>2234</v>
       </c>
@@ -21219,6 +23325,10 @@
       <c r="C553" t="s">
         <v>2232</v>
       </c>
+      <c r="D553" t="str">
+        <f t="shared" si="16"/>
+        <v>UserX509Certificate</v>
+      </c>
       <c r="E553" t="s">
         <v>2233</v>
       </c>
@@ -21228,8 +23338,12 @@
       <c r="G553" t="s">
         <v>2235</v>
       </c>
-    </row>
-    <row r="554" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H553" t="str">
+        <f t="shared" si="17"/>
+        <v>UserX509Certificate = 0x3A70,</v>
+      </c>
+    </row>
+    <row r="554" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A554" t="s">
         <v>2238</v>
       </c>
@@ -21239,6 +23353,10 @@
       <c r="C554" t="s">
         <v>2236</v>
       </c>
+      <c r="D554" t="str">
+        <f t="shared" si="16"/>
+        <v>ViewDescriptorBinary</v>
+      </c>
       <c r="E554" t="s">
         <v>2237</v>
       </c>
@@ -21248,8 +23366,12 @@
       <c r="G554" t="s">
         <v>2239</v>
       </c>
-    </row>
-    <row r="555" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H554" t="str">
+        <f t="shared" si="17"/>
+        <v>ViewDescriptorBinary = 0x7001,</v>
+      </c>
+    </row>
+    <row r="555" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A555" t="s">
         <v>2242</v>
       </c>
@@ -21259,6 +23381,10 @@
       <c r="C555" t="s">
         <v>2240</v>
       </c>
+      <c r="D555" t="str">
+        <f t="shared" si="16"/>
+        <v>ViewDescriptorName</v>
+      </c>
       <c r="E555" t="s">
         <v>2241</v>
       </c>
@@ -21268,8 +23394,12 @@
       <c r="G555" t="s">
         <v>2243</v>
       </c>
-    </row>
-    <row r="556" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H555" t="str">
+        <f t="shared" si="17"/>
+        <v>ViewDescriptorName = 0x7006,</v>
+      </c>
+    </row>
+    <row r="556" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A556" t="s">
         <v>2246</v>
       </c>
@@ -21279,6 +23409,10 @@
       <c r="C556" t="s">
         <v>2244</v>
       </c>
+      <c r="D556" t="str">
+        <f t="shared" si="16"/>
+        <v>ViewDescriptorStrings</v>
+      </c>
       <c r="E556" t="s">
         <v>2245</v>
       </c>
@@ -21288,8 +23422,12 @@
       <c r="G556" t="s">
         <v>2247</v>
       </c>
-    </row>
-    <row r="557" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H556" t="str">
+        <f t="shared" si="17"/>
+        <v>ViewDescriptorStrings = 0x7002,</v>
+      </c>
+    </row>
+    <row r="557" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A557" t="s">
         <v>2250</v>
       </c>
@@ -21299,6 +23437,10 @@
       <c r="C557" t="s">
         <v>2248</v>
       </c>
+      <c r="D557" t="str">
+        <f t="shared" si="16"/>
+        <v>ViewDescriptorVersion</v>
+      </c>
       <c r="E557" t="s">
         <v>2249</v>
       </c>
@@ -21308,8 +23450,12 @@
       <c r="G557" t="s">
         <v>2251</v>
       </c>
-    </row>
-    <row r="558" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H557" t="str">
+        <f t="shared" si="17"/>
+        <v>ViewDescriptorVersion = 0x7007,</v>
+      </c>
+    </row>
+    <row r="558" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A558" t="s">
         <v>1305</v>
       </c>
@@ -21319,6 +23465,10 @@
       <c r="C558" t="s">
         <v>2252</v>
       </c>
+      <c r="D558" t="str">
+        <f t="shared" si="16"/>
+        <v>VoiceMessageAttachmentOrder</v>
+      </c>
       <c r="E558" t="s">
         <v>2253</v>
       </c>
@@ -21328,8 +23478,12 @@
       <c r="G558" t="s">
         <v>2254</v>
       </c>
-    </row>
-    <row r="559" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H558" t="str">
+        <f t="shared" si="17"/>
+        <v>VoiceMessageAttachmentOrder = 0x6805,</v>
+      </c>
+    </row>
+    <row r="559" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A559" t="s">
         <v>1301</v>
       </c>
@@ -21339,6 +23493,10 @@
       <c r="C559" t="s">
         <v>2255</v>
       </c>
+      <c r="D559" t="str">
+        <f t="shared" si="16"/>
+        <v>VoiceMessageDuration</v>
+      </c>
       <c r="E559" t="s">
         <v>36</v>
       </c>
@@ -21348,8 +23506,12 @@
       <c r="G559" t="s">
         <v>2256</v>
       </c>
-    </row>
-    <row r="560" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H559" t="str">
+        <f t="shared" si="17"/>
+        <v>VoiceMessageDuration = 0x6801,</v>
+      </c>
+    </row>
+    <row r="560" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A560" t="s">
         <v>1293</v>
       </c>
@@ -21359,6 +23521,10 @@
       <c r="C560" t="s">
         <v>2257</v>
       </c>
+      <c r="D560" t="str">
+        <f t="shared" si="16"/>
+        <v>VoiceMessageSenderName</v>
+      </c>
       <c r="E560" t="s">
         <v>2258</v>
       </c>
@@ -21368,8 +23534,12 @@
       <c r="G560" t="s">
         <v>2259</v>
       </c>
-    </row>
-    <row r="561" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H560" t="str">
+        <f t="shared" si="17"/>
+        <v>VoiceMessageSenderName = 0x6803,</v>
+      </c>
+    </row>
+    <row r="561" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A561" t="s">
         <v>2262</v>
       </c>
@@ -21379,6 +23549,10 @@
       <c r="C561" t="s">
         <v>2260</v>
       </c>
+      <c r="D561" t="str">
+        <f t="shared" si="16"/>
+        <v>WeddingAnniversary</v>
+      </c>
       <c r="E561" t="s">
         <v>2261</v>
       </c>
@@ -21388,8 +23562,12 @@
       <c r="G561" t="s">
         <v>2263</v>
       </c>
-    </row>
-    <row r="562" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H561" t="str">
+        <f t="shared" si="17"/>
+        <v>WeddingAnniversary = 0x3A41,</v>
+      </c>
+    </row>
+    <row r="562" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A562" t="s">
         <v>1940</v>
       </c>
@@ -21399,6 +23577,10 @@
       <c r="C562" t="s">
         <v>2264</v>
       </c>
+      <c r="D562" t="str">
+        <f t="shared" si="16"/>
+        <v>WlinkAddressBookEID</v>
+      </c>
       <c r="E562" t="s">
         <v>2265</v>
       </c>
@@ -21408,8 +23590,12 @@
       <c r="G562" t="s">
         <v>2266</v>
       </c>
-    </row>
-    <row r="563" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H562" t="str">
+        <f t="shared" si="17"/>
+        <v>WlinkAddressBookEID = 0x6854,</v>
+      </c>
+    </row>
+    <row r="563" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A563" t="s">
         <v>2269</v>
       </c>
@@ -21419,6 +23605,10 @@
       <c r="C563" t="s">
         <v>2267</v>
       </c>
+      <c r="D563" t="str">
+        <f t="shared" si="16"/>
+        <v>WlinkAddressBookStoreEID</v>
+      </c>
       <c r="E563" t="s">
         <v>2268</v>
       </c>
@@ -21428,8 +23618,12 @@
       <c r="G563" t="s">
         <v>2270</v>
       </c>
-    </row>
-    <row r="564" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H563" t="str">
+        <f t="shared" si="17"/>
+        <v>WlinkAddressBookStoreEID = 0x6891,</v>
+      </c>
+    </row>
+    <row r="564" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A564" t="s">
         <v>1956</v>
       </c>
@@ -21439,6 +23633,10 @@
       <c r="C564" t="s">
         <v>2271</v>
       </c>
+      <c r="D564" t="str">
+        <f t="shared" si="16"/>
+        <v>WlinkCalendarColor</v>
+      </c>
       <c r="E564" t="s">
         <v>2272</v>
       </c>
@@ -21448,8 +23646,12 @@
       <c r="G564" t="s">
         <v>2273</v>
       </c>
-    </row>
-    <row r="565" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H564" t="str">
+        <f t="shared" si="17"/>
+        <v>WlinkCalendarColor = 0x6853,</v>
+      </c>
+    </row>
+    <row r="565" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A565" t="s">
         <v>2276</v>
       </c>
@@ -21459,6 +23661,10 @@
       <c r="C565" t="s">
         <v>2274</v>
       </c>
+      <c r="D565" t="str">
+        <f t="shared" si="16"/>
+        <v>WlinkClientID</v>
+      </c>
       <c r="E565" t="s">
         <v>2275</v>
       </c>
@@ -21468,8 +23674,12 @@
       <c r="G565" t="s">
         <v>2277</v>
       </c>
-    </row>
-    <row r="566" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H565" t="str">
+        <f t="shared" si="17"/>
+        <v>WlinkClientID = 0x6890,</v>
+      </c>
+    </row>
+    <row r="566" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A566" t="s">
         <v>2280</v>
       </c>
@@ -21479,6 +23689,10 @@
       <c r="C566" t="s">
         <v>2278</v>
       </c>
+      <c r="D566" t="str">
+        <f t="shared" si="16"/>
+        <v>WlinkEntryId</v>
+      </c>
       <c r="E566" t="s">
         <v>2279</v>
       </c>
@@ -21488,8 +23702,12 @@
       <c r="G566" t="s">
         <v>2281</v>
       </c>
-    </row>
-    <row r="567" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H566" t="str">
+        <f t="shared" si="17"/>
+        <v>WlinkEntryId = 0x684C,</v>
+      </c>
+    </row>
+    <row r="567" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A567" t="s">
         <v>1908</v>
       </c>
@@ -21499,6 +23717,10 @@
       <c r="C567" t="s">
         <v>2282</v>
       </c>
+      <c r="D567" t="str">
+        <f t="shared" si="16"/>
+        <v>WlinkFlags</v>
+      </c>
       <c r="E567" t="s">
         <v>2283</v>
       </c>
@@ -21508,8 +23730,12 @@
       <c r="G567" t="s">
         <v>2284</v>
       </c>
-    </row>
-    <row r="568" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H567" t="str">
+        <f t="shared" si="17"/>
+        <v>WlinkFlags = 0x684A,</v>
+      </c>
+    </row>
+    <row r="568" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A568" t="s">
         <v>1960</v>
       </c>
@@ -21519,6 +23745,10 @@
       <c r="C568" t="s">
         <v>2285</v>
       </c>
+      <c r="D568" t="str">
+        <f t="shared" si="16"/>
+        <v>WlinkFolderType</v>
+      </c>
       <c r="E568" t="s">
         <v>2286</v>
       </c>
@@ -21528,8 +23758,12 @@
       <c r="G568" t="s">
         <v>2287</v>
       </c>
-    </row>
-    <row r="569" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H568" t="str">
+        <f t="shared" si="17"/>
+        <v>WlinkFolderType = 0x684F,</v>
+      </c>
+    </row>
+    <row r="569" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A569" t="s">
         <v>1944</v>
       </c>
@@ -21539,6 +23773,10 @@
       <c r="C569" t="s">
         <v>2288</v>
       </c>
+      <c r="D569" t="str">
+        <f t="shared" si="16"/>
+        <v>WlinkGroupClsid</v>
+      </c>
       <c r="E569" t="s">
         <v>2289</v>
       </c>
@@ -21548,8 +23786,12 @@
       <c r="G569" t="s">
         <v>2290</v>
       </c>
-    </row>
-    <row r="570" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H569" t="str">
+        <f t="shared" si="17"/>
+        <v>WlinkGroupClsid = 0x6850,</v>
+      </c>
+    </row>
+    <row r="570" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A570" t="s">
         <v>1912</v>
       </c>
@@ -21559,6 +23801,10 @@
       <c r="C570" t="s">
         <v>2291</v>
       </c>
+      <c r="D570" t="str">
+        <f t="shared" si="16"/>
+        <v>WlinkGroupHeaderID</v>
+      </c>
       <c r="E570" t="s">
         <v>2292</v>
       </c>
@@ -21568,8 +23814,12 @@
       <c r="G570" t="s">
         <v>2293</v>
       </c>
-    </row>
-    <row r="571" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H570" t="str">
+        <f t="shared" si="17"/>
+        <v>WlinkGroupHeaderID = 0x6842,</v>
+      </c>
+    </row>
+    <row r="571" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A571" t="s">
         <v>1964</v>
       </c>
@@ -21579,6 +23829,10 @@
       <c r="C571" t="s">
         <v>2294</v>
       </c>
+      <c r="D571" t="str">
+        <f t="shared" si="16"/>
+        <v>WlinkGroupName</v>
+      </c>
       <c r="E571" t="s">
         <v>2295</v>
       </c>
@@ -21588,8 +23842,12 @@
       <c r="G571" t="s">
         <v>2296</v>
       </c>
-    </row>
-    <row r="572" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H571" t="str">
+        <f t="shared" si="17"/>
+        <v>WlinkGroupName = 0x6851,</v>
+      </c>
+    </row>
+    <row r="572" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A572" t="s">
         <v>1916</v>
       </c>
@@ -21599,6 +23857,10 @@
       <c r="C572" t="s">
         <v>2297</v>
       </c>
+      <c r="D572" t="str">
+        <f t="shared" si="16"/>
+        <v>WlinkOrdinal</v>
+      </c>
       <c r="E572" t="s">
         <v>2298</v>
       </c>
@@ -21608,8 +23870,12 @@
       <c r="G572" t="s">
         <v>2299</v>
       </c>
-    </row>
-    <row r="573" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H572" t="str">
+        <f t="shared" si="17"/>
+        <v>WlinkOrdinal = 0x684B,</v>
+      </c>
+    </row>
+    <row r="573" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A573" t="s">
         <v>2302</v>
       </c>
@@ -21619,6 +23885,10 @@
       <c r="C573" t="s">
         <v>2300</v>
       </c>
+      <c r="D573" t="str">
+        <f t="shared" si="16"/>
+        <v>WlinkRecordKey</v>
+      </c>
       <c r="E573" t="s">
         <v>2301</v>
       </c>
@@ -21628,8 +23898,12 @@
       <c r="G573" t="s">
         <v>2303</v>
       </c>
-    </row>
-    <row r="574" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H573" t="str">
+        <f t="shared" si="17"/>
+        <v>WlinkRecordKey = 0x684D,</v>
+      </c>
+    </row>
+    <row r="574" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A574" t="s">
         <v>2306</v>
       </c>
@@ -21639,6 +23913,10 @@
       <c r="C574" t="s">
         <v>2304</v>
       </c>
+      <c r="D574" t="str">
+        <f t="shared" si="16"/>
+        <v>WlinkROGroupType</v>
+      </c>
       <c r="E574" t="s">
         <v>2305</v>
       </c>
@@ -21648,8 +23926,12 @@
       <c r="G574" t="s">
         <v>2307</v>
       </c>
-    </row>
-    <row r="575" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H574" t="str">
+        <f t="shared" si="17"/>
+        <v>WlinkROGroupType = 0x6892,</v>
+      </c>
+    </row>
+    <row r="575" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A575" t="s">
         <v>860</v>
       </c>
@@ -21659,6 +23941,10 @@
       <c r="C575" t="s">
         <v>2308</v>
       </c>
+      <c r="D575" t="str">
+        <f t="shared" si="16"/>
+        <v>WlinkSaveStamp</v>
+      </c>
       <c r="E575" t="s">
         <v>2309</v>
       </c>
@@ -21668,8 +23954,12 @@
       <c r="G575" t="s">
         <v>2310</v>
       </c>
-    </row>
-    <row r="576" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H575" t="str">
+        <f t="shared" si="17"/>
+        <v>WlinkSaveStamp = 0x6847,</v>
+      </c>
+    </row>
+    <row r="576" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A576" t="s">
         <v>1948</v>
       </c>
@@ -21679,6 +23969,10 @@
       <c r="C576" t="s">
         <v>2311</v>
       </c>
+      <c r="D576" t="str">
+        <f t="shared" si="16"/>
+        <v>WlinkSection</v>
+      </c>
       <c r="E576" t="s">
         <v>2312</v>
       </c>
@@ -21688,8 +23982,12 @@
       <c r="G576" t="s">
         <v>2313</v>
       </c>
-    </row>
-    <row r="577" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H576" t="str">
+        <f t="shared" si="17"/>
+        <v>WlinkSection = 0x6852,</v>
+      </c>
+    </row>
+    <row r="577" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A577" t="s">
         <v>2316</v>
       </c>
@@ -21699,6 +23997,10 @@
       <c r="C577" t="s">
         <v>2314</v>
       </c>
+      <c r="D577" t="str">
+        <f t="shared" si="16"/>
+        <v>WlinkStoreEntryId</v>
+      </c>
       <c r="E577" t="s">
         <v>2315</v>
       </c>
@@ -21708,8 +24010,12 @@
       <c r="G577" t="s">
         <v>2317</v>
       </c>
-    </row>
-    <row r="578" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H577" t="str">
+        <f t="shared" si="17"/>
+        <v>WlinkStoreEntryId = 0x684E,</v>
+      </c>
+    </row>
+    <row r="578" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A578" t="s">
         <v>851</v>
       </c>
@@ -21719,6 +24025,10 @@
       <c r="C578" t="s">
         <v>2318</v>
       </c>
+      <c r="D578" t="str">
+        <f t="shared" si="16"/>
+        <v>WlinkType</v>
+      </c>
       <c r="E578" t="s">
         <v>2319</v>
       </c>
@@ -21727,6 +24037,10 @@
       </c>
       <c r="G578" t="s">
         <v>2320</v>
+      </c>
+      <c r="H578" t="str">
+        <f t="shared" si="17"/>
+        <v>WlinkType = 0x6849,</v>
       </c>
     </row>
   </sheetData>
